--- a/public/plantillas/Plantilla Cursos Extension CIDIAM.xlsx
+++ b/public/plantillas/Plantilla Cursos Extension CIDIAM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="13_ncr:1_{295F07E8-2423-44A1-8A43-C99DF1BADF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD95B0D4-62CB-427B-B513-4CD02BB81DBE}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="13_ncr:1_{295F07E8-2423-44A1-8A43-C99DF1BADF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B058AC03-2C3F-4F9F-9E6C-FCE59933C1F3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1360,9 +1360,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1371,6 +1368,9 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3573,7 +3573,7 @@
       <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="55" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -3653,7 +3653,7 @@
       <c r="C2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="57" t="s">
+      <c r="D2" s="56" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="35" t="s">
@@ -3727,7 +3727,7 @@
       <c r="A3" s="52"/>
       <c r="B3" s="46"/>
       <c r="C3" s="43"/>
-      <c r="D3" s="58"/>
+      <c r="D3" s="57"/>
       <c r="E3" s="44"/>
       <c r="F3" s="45"/>
       <c r="G3" s="46"/>
@@ -3755,7 +3755,7 @@
       <c r="A4" s="53"/>
       <c r="B4" s="18"/>
       <c r="C4" s="33"/>
-      <c r="D4" s="58"/>
+      <c r="D4" s="57"/>
       <c r="E4" s="19"/>
       <c r="F4" s="20"/>
       <c r="G4" s="18"/>
@@ -3783,7 +3783,7 @@
       <c r="A5" s="53"/>
       <c r="B5" s="18"/>
       <c r="C5" s="33"/>
-      <c r="D5" s="58"/>
+      <c r="D5" s="57"/>
       <c r="E5" s="19"/>
       <c r="F5" s="20"/>
       <c r="G5" s="18"/>
@@ -3811,7 +3811,7 @@
       <c r="A6" s="17"/>
       <c r="B6" s="18"/>
       <c r="C6" s="33"/>
-      <c r="D6" s="58"/>
+      <c r="D6" s="57"/>
       <c r="E6" s="19"/>
       <c r="F6" s="20"/>
       <c r="G6" s="18"/>
@@ -3839,7 +3839,7 @@
       <c r="A7" s="53"/>
       <c r="B7" s="18"/>
       <c r="C7" s="33"/>
-      <c r="D7" s="58"/>
+      <c r="D7" s="57"/>
       <c r="E7" s="19"/>
       <c r="F7" s="20"/>
       <c r="G7" s="18"/>
@@ -3867,7 +3867,7 @@
       <c r="A8" s="53"/>
       <c r="B8" s="18"/>
       <c r="C8" s="33"/>
-      <c r="D8" s="58"/>
+      <c r="D8" s="57"/>
       <c r="E8" s="19"/>
       <c r="F8" s="20"/>
       <c r="G8" s="18"/>
@@ -3895,7 +3895,7 @@
       <c r="A9" s="53"/>
       <c r="B9" s="18"/>
       <c r="C9" s="33"/>
-      <c r="D9" s="58"/>
+      <c r="D9" s="57"/>
       <c r="E9" s="19"/>
       <c r="F9" s="20"/>
       <c r="G9" s="18"/>
@@ -3923,7 +3923,7 @@
       <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="33"/>
-      <c r="D10" s="58"/>
+      <c r="D10" s="57"/>
       <c r="E10" s="19"/>
       <c r="F10" s="20"/>
       <c r="G10" s="18"/>
@@ -3951,7 +3951,7 @@
       <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="33"/>
-      <c r="D11" s="58"/>
+      <c r="D11" s="57"/>
       <c r="E11" s="19"/>
       <c r="F11" s="20"/>
       <c r="G11" s="18"/>
@@ -3979,7 +3979,7 @@
       <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="33"/>
-      <c r="D12" s="58"/>
+      <c r="D12" s="57"/>
       <c r="E12" s="19"/>
       <c r="F12" s="20"/>
       <c r="G12" s="18"/>
@@ -4007,7 +4007,7 @@
       <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="33"/>
-      <c r="D13" s="58"/>
+      <c r="D13" s="57"/>
       <c r="E13" s="19"/>
       <c r="F13" s="20"/>
       <c r="G13" s="18"/>
@@ -4035,7 +4035,7 @@
       <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="33"/>
-      <c r="D14" s="58"/>
+      <c r="D14" s="57"/>
       <c r="E14" s="19"/>
       <c r="F14" s="20"/>
       <c r="G14" s="18"/>
@@ -4063,7 +4063,7 @@
       <c r="A15" s="17"/>
       <c r="B15" s="18"/>
       <c r="C15" s="33"/>
-      <c r="D15" s="58"/>
+      <c r="D15" s="57"/>
       <c r="E15" s="19"/>
       <c r="F15" s="20"/>
       <c r="G15" s="18"/>
@@ -4091,7 +4091,7 @@
       <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="33"/>
-      <c r="D16" s="58"/>
+      <c r="D16" s="57"/>
       <c r="E16" s="19"/>
       <c r="F16" s="20"/>
       <c r="G16" s="18"/>
@@ -4119,7 +4119,7 @@
       <c r="A17" s="17"/>
       <c r="B17" s="18"/>
       <c r="C17" s="33"/>
-      <c r="D17" s="58"/>
+      <c r="D17" s="57"/>
       <c r="E17" s="19"/>
       <c r="F17" s="20"/>
       <c r="G17" s="18"/>
@@ -4147,7 +4147,7 @@
       <c r="A18" s="17"/>
       <c r="B18" s="18"/>
       <c r="C18" s="33"/>
-      <c r="D18" s="58"/>
+      <c r="D18" s="57"/>
       <c r="E18" s="19"/>
       <c r="F18" s="20"/>
       <c r="G18" s="18"/>
@@ -4175,7 +4175,7 @@
       <c r="A19" s="17"/>
       <c r="B19" s="18"/>
       <c r="C19" s="33"/>
-      <c r="D19" s="58"/>
+      <c r="D19" s="57"/>
       <c r="E19" s="19"/>
       <c r="F19" s="20"/>
       <c r="G19" s="18"/>
@@ -4203,7 +4203,7 @@
       <c r="A20" s="17"/>
       <c r="B20" s="18"/>
       <c r="C20" s="33"/>
-      <c r="D20" s="58"/>
+      <c r="D20" s="57"/>
       <c r="E20" s="19"/>
       <c r="F20" s="20"/>
       <c r="G20" s="18"/>
@@ -4231,7 +4231,7 @@
       <c r="A21" s="17"/>
       <c r="B21" s="18"/>
       <c r="C21" s="33"/>
-      <c r="D21" s="58"/>
+      <c r="D21" s="57"/>
       <c r="E21" s="19"/>
       <c r="F21" s="20"/>
       <c r="G21" s="18"/>
@@ -4259,7 +4259,7 @@
       <c r="A22" s="17"/>
       <c r="B22" s="18"/>
       <c r="C22" s="33"/>
-      <c r="D22" s="58"/>
+      <c r="D22" s="57"/>
       <c r="E22" s="19"/>
       <c r="F22" s="20"/>
       <c r="G22" s="18"/>
@@ -4287,7 +4287,7 @@
       <c r="A23" s="17"/>
       <c r="B23" s="18"/>
       <c r="C23" s="33"/>
-      <c r="D23" s="58"/>
+      <c r="D23" s="57"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="18"/>
@@ -4315,7 +4315,7 @@
       <c r="A24" s="17"/>
       <c r="B24" s="18"/>
       <c r="C24" s="33"/>
-      <c r="D24" s="58"/>
+      <c r="D24" s="57"/>
       <c r="E24" s="19"/>
       <c r="F24" s="20"/>
       <c r="G24" s="18"/>
@@ -4343,7 +4343,7 @@
       <c r="A25" s="17"/>
       <c r="B25" s="18"/>
       <c r="C25" s="33"/>
-      <c r="D25" s="58"/>
+      <c r="D25" s="57"/>
       <c r="E25" s="19"/>
       <c r="F25" s="20"/>
       <c r="G25" s="18"/>
@@ -4371,7 +4371,7 @@
       <c r="A26" s="17"/>
       <c r="B26" s="18"/>
       <c r="C26" s="33"/>
-      <c r="D26" s="58"/>
+      <c r="D26" s="57"/>
       <c r="E26" s="19"/>
       <c r="F26" s="20"/>
       <c r="G26" s="18"/>
@@ -4399,7 +4399,7 @@
       <c r="A27" s="17"/>
       <c r="B27" s="18"/>
       <c r="C27" s="33"/>
-      <c r="D27" s="58"/>
+      <c r="D27" s="57"/>
       <c r="E27" s="19"/>
       <c r="F27" s="20"/>
       <c r="G27" s="18"/>
@@ -4427,7 +4427,7 @@
       <c r="A28" s="17"/>
       <c r="B28" s="18"/>
       <c r="C28" s="33"/>
-      <c r="D28" s="58"/>
+      <c r="D28" s="57"/>
       <c r="E28" s="19"/>
       <c r="F28" s="20"/>
       <c r="G28" s="18"/>
@@ -4455,7 +4455,7 @@
       <c r="A29" s="17"/>
       <c r="B29" s="18"/>
       <c r="C29" s="33"/>
-      <c r="D29" s="58"/>
+      <c r="D29" s="57"/>
       <c r="E29" s="19"/>
       <c r="F29" s="20"/>
       <c r="G29" s="18"/>
@@ -4483,7 +4483,7 @@
       <c r="A30" s="17"/>
       <c r="B30" s="18"/>
       <c r="C30" s="33"/>
-      <c r="D30" s="58"/>
+      <c r="D30" s="57"/>
       <c r="E30" s="19"/>
       <c r="F30" s="20"/>
       <c r="G30" s="18"/>
@@ -4511,7 +4511,7 @@
       <c r="A31" s="17"/>
       <c r="B31" s="18"/>
       <c r="C31" s="33"/>
-      <c r="D31" s="58"/>
+      <c r="D31" s="57"/>
       <c r="E31" s="19"/>
       <c r="F31" s="20"/>
       <c r="G31" s="18"/>
@@ -4539,7 +4539,7 @@
       <c r="A32" s="17"/>
       <c r="B32" s="18"/>
       <c r="C32" s="33"/>
-      <c r="D32" s="58"/>
+      <c r="D32" s="57"/>
       <c r="E32" s="19"/>
       <c r="F32" s="20"/>
       <c r="G32" s="18"/>
@@ -4567,7 +4567,7 @@
       <c r="A33" s="17"/>
       <c r="B33" s="18"/>
       <c r="C33" s="33"/>
-      <c r="D33" s="58"/>
+      <c r="D33" s="57"/>
       <c r="E33" s="19"/>
       <c r="F33" s="20"/>
       <c r="G33" s="18"/>
@@ -4595,7 +4595,7 @@
       <c r="A34" s="17"/>
       <c r="B34" s="18"/>
       <c r="C34" s="33"/>
-      <c r="D34" s="58"/>
+      <c r="D34" s="57"/>
       <c r="E34" s="19"/>
       <c r="F34" s="20"/>
       <c r="G34" s="18"/>
@@ -4623,7 +4623,7 @@
       <c r="A35" s="17"/>
       <c r="B35" s="18"/>
       <c r="C35" s="33"/>
-      <c r="D35" s="58"/>
+      <c r="D35" s="57"/>
       <c r="E35" s="19"/>
       <c r="F35" s="20"/>
       <c r="G35" s="18"/>
@@ -4651,7 +4651,7 @@
       <c r="A36" s="17"/>
       <c r="B36" s="18"/>
       <c r="C36" s="33"/>
-      <c r="D36" s="58"/>
+      <c r="D36" s="57"/>
       <c r="E36" s="19"/>
       <c r="F36" s="20"/>
       <c r="G36" s="18"/>
@@ -4679,7 +4679,7 @@
       <c r="A37" s="17"/>
       <c r="B37" s="18"/>
       <c r="C37" s="33"/>
-      <c r="D37" s="58"/>
+      <c r="D37" s="57"/>
       <c r="E37" s="19"/>
       <c r="F37" s="20"/>
       <c r="G37" s="18"/>
@@ -4707,7 +4707,7 @@
       <c r="A38" s="17"/>
       <c r="B38" s="18"/>
       <c r="C38" s="33"/>
-      <c r="D38" s="58"/>
+      <c r="D38" s="57"/>
       <c r="E38" s="19"/>
       <c r="F38" s="20"/>
       <c r="G38" s="18"/>
@@ -4735,7 +4735,7 @@
       <c r="A39" s="17"/>
       <c r="B39" s="18"/>
       <c r="C39" s="33"/>
-      <c r="D39" s="58"/>
+      <c r="D39" s="57"/>
       <c r="E39" s="19"/>
       <c r="F39" s="20"/>
       <c r="G39" s="18"/>
@@ -4763,7 +4763,7 @@
       <c r="A40" s="17"/>
       <c r="B40" s="18"/>
       <c r="C40" s="33"/>
-      <c r="D40" s="58"/>
+      <c r="D40" s="57"/>
       <c r="E40" s="19"/>
       <c r="F40" s="20"/>
       <c r="G40" s="18"/>
@@ -4791,7 +4791,7 @@
       <c r="A41" s="17"/>
       <c r="B41" s="18"/>
       <c r="C41" s="33"/>
-      <c r="D41" s="58"/>
+      <c r="D41" s="57"/>
       <c r="E41" s="19"/>
       <c r="F41" s="20"/>
       <c r="G41" s="18"/>
@@ -4819,7 +4819,7 @@
       <c r="A42" s="17"/>
       <c r="B42" s="18"/>
       <c r="C42" s="33"/>
-      <c r="D42" s="58"/>
+      <c r="D42" s="57"/>
       <c r="E42" s="19"/>
       <c r="F42" s="20"/>
       <c r="G42" s="18"/>
@@ -4847,7 +4847,7 @@
       <c r="A43" s="17"/>
       <c r="B43" s="18"/>
       <c r="C43" s="33"/>
-      <c r="D43" s="58"/>
+      <c r="D43" s="57"/>
       <c r="E43" s="19"/>
       <c r="F43" s="20"/>
       <c r="G43" s="18"/>
@@ -4875,7 +4875,7 @@
       <c r="A44" s="17"/>
       <c r="B44" s="18"/>
       <c r="C44" s="33"/>
-      <c r="D44" s="58"/>
+      <c r="D44" s="57"/>
       <c r="E44" s="19"/>
       <c r="F44" s="20"/>
       <c r="G44" s="18"/>
@@ -4903,7 +4903,7 @@
       <c r="A45" s="17"/>
       <c r="B45" s="18"/>
       <c r="C45" s="33"/>
-      <c r="D45" s="58"/>
+      <c r="D45" s="57"/>
       <c r="E45" s="19"/>
       <c r="F45" s="20"/>
       <c r="G45" s="18"/>
@@ -4931,7 +4931,7 @@
       <c r="A46" s="17"/>
       <c r="B46" s="18"/>
       <c r="C46" s="33"/>
-      <c r="D46" s="58"/>
+      <c r="D46" s="57"/>
       <c r="E46" s="19"/>
       <c r="F46" s="20"/>
       <c r="G46" s="18"/>
@@ -4959,7 +4959,7 @@
       <c r="A47" s="17"/>
       <c r="B47" s="18"/>
       <c r="C47" s="33"/>
-      <c r="D47" s="58"/>
+      <c r="D47" s="57"/>
       <c r="E47" s="19"/>
       <c r="F47" s="20"/>
       <c r="G47" s="18"/>
@@ -4987,7 +4987,7 @@
       <c r="A48" s="17"/>
       <c r="B48" s="18"/>
       <c r="C48" s="33"/>
-      <c r="D48" s="58"/>
+      <c r="D48" s="57"/>
       <c r="E48" s="19"/>
       <c r="F48" s="20"/>
       <c r="G48" s="18"/>
@@ -5015,7 +5015,7 @@
       <c r="A49" s="17"/>
       <c r="B49" s="18"/>
       <c r="C49" s="33"/>
-      <c r="D49" s="58"/>
+      <c r="D49" s="57"/>
       <c r="E49" s="19"/>
       <c r="F49" s="20"/>
       <c r="G49" s="18"/>
@@ -5043,7 +5043,7 @@
       <c r="A50" s="17"/>
       <c r="B50" s="18"/>
       <c r="C50" s="33"/>
-      <c r="D50" s="58"/>
+      <c r="D50" s="57"/>
       <c r="E50" s="19"/>
       <c r="F50" s="20"/>
       <c r="G50" s="18"/>
@@ -5071,7 +5071,7 @@
       <c r="A51" s="17"/>
       <c r="B51" s="18"/>
       <c r="C51" s="33"/>
-      <c r="D51" s="58"/>
+      <c r="D51" s="57"/>
       <c r="E51" s="19"/>
       <c r="F51" s="20"/>
       <c r="G51" s="18"/>
@@ -5099,7 +5099,7 @@
       <c r="A52" s="17"/>
       <c r="B52" s="18"/>
       <c r="C52" s="33"/>
-      <c r="D52" s="58"/>
+      <c r="D52" s="57"/>
       <c r="E52" s="19"/>
       <c r="F52" s="20"/>
       <c r="G52" s="18"/>
@@ -5127,7 +5127,7 @@
       <c r="A53" s="17"/>
       <c r="B53" s="18"/>
       <c r="C53" s="33"/>
-      <c r="D53" s="58"/>
+      <c r="D53" s="57"/>
       <c r="E53" s="19"/>
       <c r="F53" s="20"/>
       <c r="G53" s="18"/>
@@ -5155,7 +5155,7 @@
       <c r="A54" s="17"/>
       <c r="B54" s="18"/>
       <c r="C54" s="33"/>
-      <c r="D54" s="58"/>
+      <c r="D54" s="57"/>
       <c r="E54" s="19"/>
       <c r="F54" s="20"/>
       <c r="G54" s="18"/>
@@ -5183,7 +5183,7 @@
       <c r="A55" s="17"/>
       <c r="B55" s="18"/>
       <c r="C55" s="33"/>
-      <c r="D55" s="58"/>
+      <c r="D55" s="57"/>
       <c r="E55" s="19"/>
       <c r="F55" s="20"/>
       <c r="G55" s="18"/>
@@ -5211,7 +5211,7 @@
       <c r="A56" s="17"/>
       <c r="B56" s="18"/>
       <c r="C56" s="33"/>
-      <c r="D56" s="58"/>
+      <c r="D56" s="57"/>
       <c r="E56" s="19"/>
       <c r="F56" s="20"/>
       <c r="G56" s="18"/>
@@ -5239,7 +5239,7 @@
       <c r="A57" s="17"/>
       <c r="B57" s="18"/>
       <c r="C57" s="33"/>
-      <c r="D57" s="58"/>
+      <c r="D57" s="57"/>
       <c r="E57" s="19"/>
       <c r="F57" s="20"/>
       <c r="G57" s="18"/>
@@ -5267,7 +5267,7 @@
       <c r="A58" s="17"/>
       <c r="B58" s="18"/>
       <c r="C58" s="33"/>
-      <c r="D58" s="58"/>
+      <c r="D58" s="57"/>
       <c r="E58" s="19"/>
       <c r="F58" s="20"/>
       <c r="G58" s="18"/>
@@ -5295,7 +5295,7 @@
       <c r="A59" s="17"/>
       <c r="B59" s="18"/>
       <c r="C59" s="33"/>
-      <c r="D59" s="58"/>
+      <c r="D59" s="57"/>
       <c r="E59" s="19"/>
       <c r="F59" s="20"/>
       <c r="G59" s="18"/>
@@ -5323,7 +5323,7 @@
       <c r="A60" s="17"/>
       <c r="B60" s="18"/>
       <c r="C60" s="33"/>
-      <c r="D60" s="58"/>
+      <c r="D60" s="57"/>
       <c r="E60" s="19"/>
       <c r="F60" s="20"/>
       <c r="G60" s="18"/>
@@ -5351,7 +5351,7 @@
       <c r="A61" s="17"/>
       <c r="B61" s="18"/>
       <c r="C61" s="33"/>
-      <c r="D61" s="58"/>
+      <c r="D61" s="57"/>
       <c r="E61" s="19"/>
       <c r="F61" s="20"/>
       <c r="G61" s="18"/>
@@ -5379,7 +5379,7 @@
       <c r="A62" s="17"/>
       <c r="B62" s="18"/>
       <c r="C62" s="33"/>
-      <c r="D62" s="58"/>
+      <c r="D62" s="57"/>
       <c r="E62" s="19"/>
       <c r="F62" s="20"/>
       <c r="G62" s="18"/>
@@ -5407,7 +5407,7 @@
       <c r="A63" s="17"/>
       <c r="B63" s="18"/>
       <c r="C63" s="33"/>
-      <c r="D63" s="58"/>
+      <c r="D63" s="57"/>
       <c r="E63" s="19"/>
       <c r="F63" s="20"/>
       <c r="G63" s="18"/>
@@ -5435,7 +5435,7 @@
       <c r="A64" s="17"/>
       <c r="B64" s="18"/>
       <c r="C64" s="33"/>
-      <c r="D64" s="58"/>
+      <c r="D64" s="57"/>
       <c r="E64" s="19"/>
       <c r="F64" s="20"/>
       <c r="G64" s="18"/>
@@ -5463,7 +5463,7 @@
       <c r="A65" s="17"/>
       <c r="B65" s="18"/>
       <c r="C65" s="33"/>
-      <c r="D65" s="58"/>
+      <c r="D65" s="57"/>
       <c r="E65" s="19"/>
       <c r="F65" s="20"/>
       <c r="G65" s="18"/>
@@ -5491,7 +5491,7 @@
       <c r="A66" s="17"/>
       <c r="B66" s="18"/>
       <c r="C66" s="33"/>
-      <c r="D66" s="58"/>
+      <c r="D66" s="57"/>
       <c r="E66" s="19"/>
       <c r="F66" s="20"/>
       <c r="G66" s="18"/>
@@ -5519,7 +5519,7 @@
       <c r="A67" s="17"/>
       <c r="B67" s="18"/>
       <c r="C67" s="33"/>
-      <c r="D67" s="58"/>
+      <c r="D67" s="57"/>
       <c r="E67" s="19"/>
       <c r="F67" s="20"/>
       <c r="G67" s="18"/>
@@ -5547,7 +5547,7 @@
       <c r="A68" s="17"/>
       <c r="B68" s="18"/>
       <c r="C68" s="33"/>
-      <c r="D68" s="58"/>
+      <c r="D68" s="57"/>
       <c r="E68" s="19"/>
       <c r="F68" s="20"/>
       <c r="G68" s="18"/>
@@ -5575,7 +5575,7 @@
       <c r="A69" s="17"/>
       <c r="B69" s="18"/>
       <c r="C69" s="33"/>
-      <c r="D69" s="58"/>
+      <c r="D69" s="57"/>
       <c r="E69" s="19"/>
       <c r="F69" s="20"/>
       <c r="G69" s="18"/>
@@ -5603,7 +5603,7 @@
       <c r="A70" s="17"/>
       <c r="B70" s="18"/>
       <c r="C70" s="33"/>
-      <c r="D70" s="58"/>
+      <c r="D70" s="57"/>
       <c r="E70" s="19"/>
       <c r="F70" s="20"/>
       <c r="G70" s="18"/>
@@ -5631,7 +5631,7 @@
       <c r="A71" s="17"/>
       <c r="B71" s="18"/>
       <c r="C71" s="33"/>
-      <c r="D71" s="58"/>
+      <c r="D71" s="57"/>
       <c r="E71" s="19"/>
       <c r="F71" s="20"/>
       <c r="G71" s="18"/>
@@ -5659,7 +5659,7 @@
       <c r="A72" s="17"/>
       <c r="B72" s="18"/>
       <c r="C72" s="33"/>
-      <c r="D72" s="58"/>
+      <c r="D72" s="57"/>
       <c r="E72" s="19"/>
       <c r="F72" s="20"/>
       <c r="G72" s="18"/>
@@ -5687,7 +5687,7 @@
       <c r="A73" s="17"/>
       <c r="B73" s="18"/>
       <c r="C73" s="33"/>
-      <c r="D73" s="58"/>
+      <c r="D73" s="57"/>
       <c r="E73" s="19"/>
       <c r="F73" s="20"/>
       <c r="G73" s="18"/>
@@ -5715,7 +5715,7 @@
       <c r="A74" s="17"/>
       <c r="B74" s="18"/>
       <c r="C74" s="33"/>
-      <c r="D74" s="58"/>
+      <c r="D74" s="57"/>
       <c r="E74" s="19"/>
       <c r="F74" s="20"/>
       <c r="G74" s="18"/>
@@ -5743,7 +5743,7 @@
       <c r="A75" s="17"/>
       <c r="B75" s="18"/>
       <c r="C75" s="33"/>
-      <c r="D75" s="58"/>
+      <c r="D75" s="57"/>
       <c r="E75" s="19"/>
       <c r="F75" s="20"/>
       <c r="G75" s="18"/>
@@ -5771,7 +5771,7 @@
       <c r="A76" s="17"/>
       <c r="B76" s="18"/>
       <c r="C76" s="33"/>
-      <c r="D76" s="58"/>
+      <c r="D76" s="57"/>
       <c r="E76" s="19"/>
       <c r="F76" s="20"/>
       <c r="G76" s="18"/>
@@ -5799,7 +5799,7 @@
       <c r="A77" s="17"/>
       <c r="B77" s="18"/>
       <c r="C77" s="33"/>
-      <c r="D77" s="58"/>
+      <c r="D77" s="57"/>
       <c r="E77" s="19"/>
       <c r="F77" s="20"/>
       <c r="G77" s="18"/>
@@ -5827,7 +5827,7 @@
       <c r="A78" s="17"/>
       <c r="B78" s="18"/>
       <c r="C78" s="33"/>
-      <c r="D78" s="58"/>
+      <c r="D78" s="57"/>
       <c r="E78" s="19"/>
       <c r="F78" s="20"/>
       <c r="G78" s="18"/>
@@ -5855,7 +5855,7 @@
       <c r="A79" s="17"/>
       <c r="B79" s="18"/>
       <c r="C79" s="33"/>
-      <c r="D79" s="58"/>
+      <c r="D79" s="57"/>
       <c r="E79" s="19"/>
       <c r="F79" s="20"/>
       <c r="G79" s="18"/>
@@ -5883,7 +5883,7 @@
       <c r="A80" s="17"/>
       <c r="B80" s="18"/>
       <c r="C80" s="33"/>
-      <c r="D80" s="58"/>
+      <c r="D80" s="57"/>
       <c r="E80" s="19"/>
       <c r="F80" s="20"/>
       <c r="G80" s="18"/>
@@ -5911,7 +5911,7 @@
       <c r="A81" s="17"/>
       <c r="B81" s="18"/>
       <c r="C81" s="33"/>
-      <c r="D81" s="58"/>
+      <c r="D81" s="57"/>
       <c r="E81" s="19"/>
       <c r="F81" s="20"/>
       <c r="G81" s="18"/>
@@ -5939,7 +5939,7 @@
       <c r="A82" s="17"/>
       <c r="B82" s="18"/>
       <c r="C82" s="33"/>
-      <c r="D82" s="58"/>
+      <c r="D82" s="57"/>
       <c r="E82" s="19"/>
       <c r="F82" s="20"/>
       <c r="G82" s="18"/>
@@ -5967,7 +5967,7 @@
       <c r="A83" s="17"/>
       <c r="B83" s="18"/>
       <c r="C83" s="33"/>
-      <c r="D83" s="58"/>
+      <c r="D83" s="57"/>
       <c r="E83" s="19"/>
       <c r="F83" s="20"/>
       <c r="G83" s="18"/>
@@ -5995,7 +5995,7 @@
       <c r="A84" s="17"/>
       <c r="B84" s="18"/>
       <c r="C84" s="33"/>
-      <c r="D84" s="58"/>
+      <c r="D84" s="57"/>
       <c r="E84" s="19"/>
       <c r="F84" s="20"/>
       <c r="G84" s="18"/>
@@ -6023,7 +6023,7 @@
       <c r="A85" s="17"/>
       <c r="B85" s="18"/>
       <c r="C85" s="33"/>
-      <c r="D85" s="58"/>
+      <c r="D85" s="57"/>
       <c r="E85" s="19"/>
       <c r="F85" s="20"/>
       <c r="G85" s="18"/>
@@ -6051,7 +6051,7 @@
       <c r="A86" s="17"/>
       <c r="B86" s="18"/>
       <c r="C86" s="33"/>
-      <c r="D86" s="58"/>
+      <c r="D86" s="57"/>
       <c r="E86" s="19"/>
       <c r="F86" s="20"/>
       <c r="G86" s="18"/>
@@ -6079,7 +6079,7 @@
       <c r="A87" s="17"/>
       <c r="B87" s="18"/>
       <c r="C87" s="33"/>
-      <c r="D87" s="58"/>
+      <c r="D87" s="57"/>
       <c r="E87" s="19"/>
       <c r="F87" s="20"/>
       <c r="G87" s="18"/>
@@ -6107,7 +6107,7 @@
       <c r="A88" s="17"/>
       <c r="B88" s="18"/>
       <c r="C88" s="33"/>
-      <c r="D88" s="58"/>
+      <c r="D88" s="57"/>
       <c r="E88" s="19"/>
       <c r="F88" s="20"/>
       <c r="G88" s="18"/>
@@ -6135,7 +6135,7 @@
       <c r="A89" s="17"/>
       <c r="B89" s="18"/>
       <c r="C89" s="33"/>
-      <c r="D89" s="58"/>
+      <c r="D89" s="57"/>
       <c r="E89" s="19"/>
       <c r="F89" s="20"/>
       <c r="G89" s="18"/>
@@ -6163,7 +6163,7 @@
       <c r="A90" s="17"/>
       <c r="B90" s="18"/>
       <c r="C90" s="33"/>
-      <c r="D90" s="58"/>
+      <c r="D90" s="57"/>
       <c r="E90" s="19"/>
       <c r="F90" s="20"/>
       <c r="G90" s="18"/>
@@ -6191,7 +6191,7 @@
       <c r="A91" s="17"/>
       <c r="B91" s="18"/>
       <c r="C91" s="33"/>
-      <c r="D91" s="58"/>
+      <c r="D91" s="57"/>
       <c r="E91" s="19"/>
       <c r="F91" s="20"/>
       <c r="G91" s="18"/>
@@ -6219,7 +6219,7 @@
       <c r="A92" s="17"/>
       <c r="B92" s="18"/>
       <c r="C92" s="33"/>
-      <c r="D92" s="58"/>
+      <c r="D92" s="57"/>
       <c r="E92" s="19"/>
       <c r="F92" s="20"/>
       <c r="G92" s="18"/>
@@ -6247,7 +6247,7 @@
       <c r="A93" s="17"/>
       <c r="B93" s="18"/>
       <c r="C93" s="33"/>
-      <c r="D93" s="58"/>
+      <c r="D93" s="57"/>
       <c r="E93" s="19"/>
       <c r="F93" s="20"/>
       <c r="G93" s="18"/>
@@ -6275,7 +6275,7 @@
       <c r="A94" s="17"/>
       <c r="B94" s="18"/>
       <c r="C94" s="33"/>
-      <c r="D94" s="58"/>
+      <c r="D94" s="57"/>
       <c r="E94" s="19"/>
       <c r="F94" s="20"/>
       <c r="G94" s="18"/>
@@ -6303,7 +6303,7 @@
       <c r="A95" s="17"/>
       <c r="B95" s="18"/>
       <c r="C95" s="33"/>
-      <c r="D95" s="58"/>
+      <c r="D95" s="57"/>
       <c r="E95" s="19"/>
       <c r="F95" s="20"/>
       <c r="G95" s="18"/>
@@ -6331,7 +6331,7 @@
       <c r="A96" s="17"/>
       <c r="B96" s="18"/>
       <c r="C96" s="33"/>
-      <c r="D96" s="58"/>
+      <c r="D96" s="57"/>
       <c r="E96" s="19"/>
       <c r="F96" s="20"/>
       <c r="G96" s="18"/>
@@ -6359,7 +6359,7 @@
       <c r="A97" s="17"/>
       <c r="B97" s="18"/>
       <c r="C97" s="33"/>
-      <c r="D97" s="58"/>
+      <c r="D97" s="57"/>
       <c r="E97" s="19"/>
       <c r="F97" s="20"/>
       <c r="G97" s="18"/>
@@ -6387,7 +6387,7 @@
       <c r="A98" s="17"/>
       <c r="B98" s="18"/>
       <c r="C98" s="33"/>
-      <c r="D98" s="58"/>
+      <c r="D98" s="57"/>
       <c r="E98" s="19"/>
       <c r="F98" s="20"/>
       <c r="G98" s="18"/>
@@ -6415,7 +6415,7 @@
       <c r="A99" s="17"/>
       <c r="B99" s="18"/>
       <c r="C99" s="33"/>
-      <c r="D99" s="58"/>
+      <c r="D99" s="57"/>
       <c r="E99" s="19"/>
       <c r="F99" s="20"/>
       <c r="G99" s="18"/>
@@ -6443,7 +6443,7 @@
       <c r="A100" s="17"/>
       <c r="B100" s="18"/>
       <c r="C100" s="33"/>
-      <c r="D100" s="58"/>
+      <c r="D100" s="57"/>
       <c r="E100" s="19"/>
       <c r="F100" s="20"/>
       <c r="G100" s="18"/>
@@ -6471,7 +6471,7 @@
       <c r="A101" s="17"/>
       <c r="B101" s="18"/>
       <c r="C101" s="33"/>
-      <c r="D101" s="58"/>
+      <c r="D101" s="57"/>
       <c r="E101" s="19"/>
       <c r="F101" s="20"/>
       <c r="G101" s="18"/>
@@ -6499,7 +6499,7 @@
       <c r="A102" s="17"/>
       <c r="B102" s="18"/>
       <c r="C102" s="33"/>
-      <c r="D102" s="58"/>
+      <c r="D102" s="57"/>
       <c r="E102" s="19"/>
       <c r="F102" s="20"/>
       <c r="G102" s="18"/>
@@ -6527,7 +6527,7 @@
       <c r="A103" s="17"/>
       <c r="B103" s="18"/>
       <c r="C103" s="33"/>
-      <c r="D103" s="58"/>
+      <c r="D103" s="57"/>
       <c r="E103" s="19"/>
       <c r="F103" s="20"/>
       <c r="G103" s="18"/>
@@ -6555,7 +6555,7 @@
       <c r="A104" s="17"/>
       <c r="B104" s="18"/>
       <c r="C104" s="33"/>
-      <c r="D104" s="58"/>
+      <c r="D104" s="57"/>
       <c r="E104" s="19"/>
       <c r="F104" s="20"/>
       <c r="G104" s="18"/>
@@ -6583,7 +6583,7 @@
       <c r="A105" s="17"/>
       <c r="B105" s="18"/>
       <c r="C105" s="33"/>
-      <c r="D105" s="58"/>
+      <c r="D105" s="57"/>
       <c r="E105" s="19"/>
       <c r="F105" s="20"/>
       <c r="G105" s="18"/>
@@ -6611,7 +6611,7 @@
       <c r="A106" s="17"/>
       <c r="B106" s="18"/>
       <c r="C106" s="33"/>
-      <c r="D106" s="58"/>
+      <c r="D106" s="57"/>
       <c r="E106" s="19"/>
       <c r="F106" s="20"/>
       <c r="G106" s="18"/>
@@ -6639,7 +6639,7 @@
       <c r="A107" s="17"/>
       <c r="B107" s="18"/>
       <c r="C107" s="33"/>
-      <c r="D107" s="58"/>
+      <c r="D107" s="57"/>
       <c r="E107" s="19"/>
       <c r="F107" s="20"/>
       <c r="G107" s="18"/>
@@ -6667,7 +6667,7 @@
       <c r="A108" s="17"/>
       <c r="B108" s="18"/>
       <c r="C108" s="33"/>
-      <c r="D108" s="58"/>
+      <c r="D108" s="57"/>
       <c r="E108" s="19"/>
       <c r="F108" s="20"/>
       <c r="G108" s="18"/>
@@ -6695,7 +6695,7 @@
       <c r="A109" s="17"/>
       <c r="B109" s="18"/>
       <c r="C109" s="33"/>
-      <c r="D109" s="58"/>
+      <c r="D109" s="57"/>
       <c r="E109" s="19"/>
       <c r="F109" s="20"/>
       <c r="G109" s="18"/>
@@ -6723,7 +6723,7 @@
       <c r="A110" s="17"/>
       <c r="B110" s="18"/>
       <c r="C110" s="33"/>
-      <c r="D110" s="58"/>
+      <c r="D110" s="57"/>
       <c r="E110" s="19"/>
       <c r="F110" s="20"/>
       <c r="G110" s="18"/>
@@ -6751,7 +6751,7 @@
       <c r="A111" s="17"/>
       <c r="B111" s="18"/>
       <c r="C111" s="33"/>
-      <c r="D111" s="58"/>
+      <c r="D111" s="57"/>
       <c r="E111" s="19"/>
       <c r="F111" s="20"/>
       <c r="G111" s="18"/>
@@ -6779,7 +6779,7 @@
       <c r="A112" s="17"/>
       <c r="B112" s="18"/>
       <c r="C112" s="33"/>
-      <c r="D112" s="58"/>
+      <c r="D112" s="57"/>
       <c r="E112" s="19"/>
       <c r="F112" s="20"/>
       <c r="G112" s="18"/>
@@ -6807,7 +6807,7 @@
       <c r="A113" s="17"/>
       <c r="B113" s="18"/>
       <c r="C113" s="33"/>
-      <c r="D113" s="58"/>
+      <c r="D113" s="57"/>
       <c r="E113" s="19"/>
       <c r="F113" s="20"/>
       <c r="G113" s="18"/>
@@ -6835,7 +6835,7 @@
       <c r="A114" s="17"/>
       <c r="B114" s="18"/>
       <c r="C114" s="33"/>
-      <c r="D114" s="58"/>
+      <c r="D114" s="57"/>
       <c r="E114" s="19"/>
       <c r="F114" s="20"/>
       <c r="G114" s="18"/>
@@ -6863,7 +6863,7 @@
       <c r="A115" s="17"/>
       <c r="B115" s="18"/>
       <c r="C115" s="33"/>
-      <c r="D115" s="58"/>
+      <c r="D115" s="57"/>
       <c r="E115" s="19"/>
       <c r="F115" s="20"/>
       <c r="G115" s="18"/>
@@ -6891,7 +6891,7 @@
       <c r="A116" s="17"/>
       <c r="B116" s="18"/>
       <c r="C116" s="33"/>
-      <c r="D116" s="58"/>
+      <c r="D116" s="57"/>
       <c r="E116" s="19"/>
       <c r="F116" s="20"/>
       <c r="G116" s="18"/>
@@ -6919,7 +6919,7 @@
       <c r="A117" s="17"/>
       <c r="B117" s="18"/>
       <c r="C117" s="33"/>
-      <c r="D117" s="58"/>
+      <c r="D117" s="57"/>
       <c r="E117" s="19"/>
       <c r="F117" s="20"/>
       <c r="G117" s="18"/>
@@ -6947,7 +6947,7 @@
       <c r="A118" s="17"/>
       <c r="B118" s="18"/>
       <c r="C118" s="33"/>
-      <c r="D118" s="58"/>
+      <c r="D118" s="57"/>
       <c r="E118" s="19"/>
       <c r="F118" s="20"/>
       <c r="G118" s="18"/>
@@ -6975,7 +6975,7 @@
       <c r="A119" s="17"/>
       <c r="B119" s="18"/>
       <c r="C119" s="33"/>
-      <c r="D119" s="58"/>
+      <c r="D119" s="57"/>
       <c r="E119" s="19"/>
       <c r="F119" s="20"/>
       <c r="G119" s="18"/>
@@ -7003,7 +7003,7 @@
       <c r="A120" s="17"/>
       <c r="B120" s="18"/>
       <c r="C120" s="33"/>
-      <c r="D120" s="58"/>
+      <c r="D120" s="57"/>
       <c r="E120" s="19"/>
       <c r="F120" s="20"/>
       <c r="G120" s="18"/>
@@ -7031,7 +7031,7 @@
       <c r="A121" s="17"/>
       <c r="B121" s="18"/>
       <c r="C121" s="33"/>
-      <c r="D121" s="58"/>
+      <c r="D121" s="57"/>
       <c r="E121" s="19"/>
       <c r="F121" s="20"/>
       <c r="G121" s="18"/>
@@ -7059,7 +7059,7 @@
       <c r="A122" s="17"/>
       <c r="B122" s="18"/>
       <c r="C122" s="33"/>
-      <c r="D122" s="58"/>
+      <c r="D122" s="57"/>
       <c r="E122" s="19"/>
       <c r="F122" s="20"/>
       <c r="G122" s="18"/>
@@ -7087,7 +7087,7 @@
       <c r="A123" s="17"/>
       <c r="B123" s="18"/>
       <c r="C123" s="33"/>
-      <c r="D123" s="58"/>
+      <c r="D123" s="57"/>
       <c r="E123" s="19"/>
       <c r="F123" s="20"/>
       <c r="G123" s="18"/>
@@ -7115,7 +7115,7 @@
       <c r="A124" s="17"/>
       <c r="B124" s="18"/>
       <c r="C124" s="33"/>
-      <c r="D124" s="58"/>
+      <c r="D124" s="57"/>
       <c r="E124" s="19"/>
       <c r="F124" s="20"/>
       <c r="G124" s="18"/>
@@ -7143,7 +7143,7 @@
       <c r="A125" s="17"/>
       <c r="B125" s="18"/>
       <c r="C125" s="33"/>
-      <c r="D125" s="58"/>
+      <c r="D125" s="57"/>
       <c r="E125" s="19"/>
       <c r="F125" s="20"/>
       <c r="G125" s="18"/>
@@ -7171,7 +7171,7 @@
       <c r="A126" s="17"/>
       <c r="B126" s="18"/>
       <c r="C126" s="33"/>
-      <c r="D126" s="58"/>
+      <c r="D126" s="57"/>
       <c r="E126" s="19"/>
       <c r="F126" s="20"/>
       <c r="G126" s="18"/>
@@ -7199,7 +7199,7 @@
       <c r="A127" s="17"/>
       <c r="B127" s="18"/>
       <c r="C127" s="33"/>
-      <c r="D127" s="58"/>
+      <c r="D127" s="57"/>
       <c r="E127" s="19"/>
       <c r="F127" s="20"/>
       <c r="G127" s="18"/>
@@ -7227,7 +7227,7 @@
       <c r="A128" s="17"/>
       <c r="B128" s="18"/>
       <c r="C128" s="33"/>
-      <c r="D128" s="58"/>
+      <c r="D128" s="57"/>
       <c r="E128" s="19"/>
       <c r="F128" s="20"/>
       <c r="G128" s="18"/>
@@ -7255,7 +7255,7 @@
       <c r="A129" s="17"/>
       <c r="B129" s="18"/>
       <c r="C129" s="33"/>
-      <c r="D129" s="58"/>
+      <c r="D129" s="57"/>
       <c r="E129" s="19"/>
       <c r="F129" s="20"/>
       <c r="G129" s="18"/>
@@ -7283,7 +7283,7 @@
       <c r="A130" s="17"/>
       <c r="B130" s="18"/>
       <c r="C130" s="33"/>
-      <c r="D130" s="58"/>
+      <c r="D130" s="57"/>
       <c r="E130" s="19"/>
       <c r="F130" s="20"/>
       <c r="G130" s="18"/>
@@ -7311,7 +7311,7 @@
       <c r="A131" s="17"/>
       <c r="B131" s="18"/>
       <c r="C131" s="33"/>
-      <c r="D131" s="58"/>
+      <c r="D131" s="57"/>
       <c r="E131" s="19"/>
       <c r="F131" s="20"/>
       <c r="G131" s="18"/>
@@ -7339,7 +7339,7 @@
       <c r="A132" s="17"/>
       <c r="B132" s="18"/>
       <c r="C132" s="33"/>
-      <c r="D132" s="58"/>
+      <c r="D132" s="57"/>
       <c r="E132" s="19"/>
       <c r="F132" s="20"/>
       <c r="G132" s="18"/>
@@ -7367,7 +7367,7 @@
       <c r="A133" s="17"/>
       <c r="B133" s="18"/>
       <c r="C133" s="33"/>
-      <c r="D133" s="58"/>
+      <c r="D133" s="57"/>
       <c r="E133" s="19"/>
       <c r="F133" s="20"/>
       <c r="G133" s="18"/>
@@ -7395,7 +7395,7 @@
       <c r="A134" s="17"/>
       <c r="B134" s="18"/>
       <c r="C134" s="33"/>
-      <c r="D134" s="58"/>
+      <c r="D134" s="57"/>
       <c r="E134" s="19"/>
       <c r="F134" s="20"/>
       <c r="G134" s="18"/>
@@ -7423,7 +7423,7 @@
       <c r="A135" s="17"/>
       <c r="B135" s="18"/>
       <c r="C135" s="33"/>
-      <c r="D135" s="58"/>
+      <c r="D135" s="57"/>
       <c r="E135" s="19"/>
       <c r="F135" s="20"/>
       <c r="G135" s="18"/>
@@ -7451,7 +7451,7 @@
       <c r="A136" s="17"/>
       <c r="B136" s="18"/>
       <c r="C136" s="33"/>
-      <c r="D136" s="58"/>
+      <c r="D136" s="57"/>
       <c r="E136" s="19"/>
       <c r="F136" s="20"/>
       <c r="G136" s="18"/>
@@ -7479,7 +7479,7 @@
       <c r="A137" s="17"/>
       <c r="B137" s="18"/>
       <c r="C137" s="33"/>
-      <c r="D137" s="58"/>
+      <c r="D137" s="57"/>
       <c r="E137" s="19"/>
       <c r="F137" s="20"/>
       <c r="G137" s="18"/>
@@ -7507,7 +7507,7 @@
       <c r="A138" s="17"/>
       <c r="B138" s="18"/>
       <c r="C138" s="33"/>
-      <c r="D138" s="58"/>
+      <c r="D138" s="57"/>
       <c r="E138" s="19"/>
       <c r="F138" s="20"/>
       <c r="G138" s="18"/>
@@ -7535,7 +7535,7 @@
       <c r="A139" s="17"/>
       <c r="B139" s="18"/>
       <c r="C139" s="33"/>
-      <c r="D139" s="58"/>
+      <c r="D139" s="57"/>
       <c r="E139" s="19"/>
       <c r="F139" s="20"/>
       <c r="G139" s="18"/>
@@ -7563,7 +7563,7 @@
       <c r="A140" s="17"/>
       <c r="B140" s="18"/>
       <c r="C140" s="33"/>
-      <c r="D140" s="58"/>
+      <c r="D140" s="57"/>
       <c r="E140" s="19"/>
       <c r="F140" s="20"/>
       <c r="G140" s="18"/>
@@ -7591,7 +7591,7 @@
       <c r="A141" s="17"/>
       <c r="B141" s="18"/>
       <c r="C141" s="33"/>
-      <c r="D141" s="58"/>
+      <c r="D141" s="57"/>
       <c r="E141" s="19"/>
       <c r="F141" s="20"/>
       <c r="G141" s="18"/>
@@ -7619,7 +7619,7 @@
       <c r="A142" s="17"/>
       <c r="B142" s="18"/>
       <c r="C142" s="33"/>
-      <c r="D142" s="58"/>
+      <c r="D142" s="57"/>
       <c r="E142" s="19"/>
       <c r="F142" s="20"/>
       <c r="G142" s="18"/>
@@ -7647,7 +7647,7 @@
       <c r="A143" s="17"/>
       <c r="B143" s="18"/>
       <c r="C143" s="33"/>
-      <c r="D143" s="58"/>
+      <c r="D143" s="57"/>
       <c r="E143" s="19"/>
       <c r="F143" s="20"/>
       <c r="G143" s="18"/>
@@ -7675,7 +7675,7 @@
       <c r="A144" s="17"/>
       <c r="B144" s="18"/>
       <c r="C144" s="33"/>
-      <c r="D144" s="58"/>
+      <c r="D144" s="57"/>
       <c r="E144" s="19"/>
       <c r="F144" s="20"/>
       <c r="G144" s="18"/>
@@ -7703,7 +7703,7 @@
       <c r="A145" s="17"/>
       <c r="B145" s="18"/>
       <c r="C145" s="33"/>
-      <c r="D145" s="58"/>
+      <c r="D145" s="57"/>
       <c r="E145" s="19"/>
       <c r="F145" s="20"/>
       <c r="G145" s="18"/>
@@ -7731,7 +7731,7 @@
       <c r="A146" s="17"/>
       <c r="B146" s="18"/>
       <c r="C146" s="33"/>
-      <c r="D146" s="58"/>
+      <c r="D146" s="57"/>
       <c r="E146" s="19"/>
       <c r="F146" s="20"/>
       <c r="G146" s="18"/>
@@ -7759,7 +7759,7 @@
       <c r="A147" s="17"/>
       <c r="B147" s="18"/>
       <c r="C147" s="33"/>
-      <c r="D147" s="58"/>
+      <c r="D147" s="57"/>
       <c r="E147" s="19"/>
       <c r="F147" s="20"/>
       <c r="G147" s="18"/>
@@ -7787,7 +7787,7 @@
       <c r="A148" s="17"/>
       <c r="B148" s="18"/>
       <c r="C148" s="33"/>
-      <c r="D148" s="58"/>
+      <c r="D148" s="57"/>
       <c r="E148" s="19"/>
       <c r="F148" s="20"/>
       <c r="G148" s="18"/>
@@ -7815,7 +7815,7 @@
       <c r="A149" s="17"/>
       <c r="B149" s="18"/>
       <c r="C149" s="33"/>
-      <c r="D149" s="58"/>
+      <c r="D149" s="57"/>
       <c r="E149" s="19"/>
       <c r="F149" s="20"/>
       <c r="G149" s="18"/>
@@ -7843,7 +7843,7 @@
       <c r="A150" s="17"/>
       <c r="B150" s="18"/>
       <c r="C150" s="33"/>
-      <c r="D150" s="58"/>
+      <c r="D150" s="57"/>
       <c r="E150" s="19"/>
       <c r="F150" s="20"/>
       <c r="G150" s="18"/>
@@ -7871,7 +7871,7 @@
       <c r="A151" s="17"/>
       <c r="B151" s="18"/>
       <c r="C151" s="33"/>
-      <c r="D151" s="58"/>
+      <c r="D151" s="57"/>
       <c r="E151" s="19"/>
       <c r="F151" s="20"/>
       <c r="G151" s="18"/>
@@ -7899,7 +7899,7 @@
       <c r="A152" s="17"/>
       <c r="B152" s="18"/>
       <c r="C152" s="33"/>
-      <c r="D152" s="58"/>
+      <c r="D152" s="57"/>
       <c r="E152" s="19"/>
       <c r="F152" s="20"/>
       <c r="G152" s="18"/>
@@ -7927,7 +7927,7 @@
       <c r="A153" s="17"/>
       <c r="B153" s="18"/>
       <c r="C153" s="33"/>
-      <c r="D153" s="58"/>
+      <c r="D153" s="57"/>
       <c r="E153" s="19"/>
       <c r="F153" s="20"/>
       <c r="G153" s="18"/>
@@ -7955,7 +7955,7 @@
       <c r="A154" s="17"/>
       <c r="B154" s="18"/>
       <c r="C154" s="33"/>
-      <c r="D154" s="58"/>
+      <c r="D154" s="57"/>
       <c r="E154" s="19"/>
       <c r="F154" s="20"/>
       <c r="G154" s="18"/>
@@ -7983,7 +7983,7 @@
       <c r="A155" s="17"/>
       <c r="B155" s="18"/>
       <c r="C155" s="33"/>
-      <c r="D155" s="58"/>
+      <c r="D155" s="57"/>
       <c r="E155" s="19"/>
       <c r="F155" s="20"/>
       <c r="G155" s="18"/>
@@ -8011,7 +8011,7 @@
       <c r="A156" s="17"/>
       <c r="B156" s="18"/>
       <c r="C156" s="33"/>
-      <c r="D156" s="58"/>
+      <c r="D156" s="57"/>
       <c r="E156" s="19"/>
       <c r="F156" s="20"/>
       <c r="G156" s="18"/>
@@ -8039,7 +8039,7 @@
       <c r="A157" s="17"/>
       <c r="B157" s="18"/>
       <c r="C157" s="33"/>
-      <c r="D157" s="58"/>
+      <c r="D157" s="57"/>
       <c r="E157" s="19"/>
       <c r="F157" s="20"/>
       <c r="G157" s="18"/>
@@ -8067,7 +8067,7 @@
       <c r="A158" s="17"/>
       <c r="B158" s="18"/>
       <c r="C158" s="33"/>
-      <c r="D158" s="58"/>
+      <c r="D158" s="57"/>
       <c r="E158" s="19"/>
       <c r="F158" s="20"/>
       <c r="G158" s="18"/>
@@ -8095,7 +8095,7 @@
       <c r="A159" s="17"/>
       <c r="B159" s="18"/>
       <c r="C159" s="33"/>
-      <c r="D159" s="58"/>
+      <c r="D159" s="57"/>
       <c r="E159" s="19"/>
       <c r="F159" s="20"/>
       <c r="G159" s="18"/>
@@ -8123,7 +8123,7 @@
       <c r="A160" s="17"/>
       <c r="B160" s="18"/>
       <c r="C160" s="33"/>
-      <c r="D160" s="58"/>
+      <c r="D160" s="57"/>
       <c r="E160" s="19"/>
       <c r="F160" s="20"/>
       <c r="G160" s="18"/>
@@ -8151,7 +8151,7 @@
       <c r="A161" s="17"/>
       <c r="B161" s="18"/>
       <c r="C161" s="33"/>
-      <c r="D161" s="58"/>
+      <c r="D161" s="57"/>
       <c r="E161" s="19"/>
       <c r="F161" s="20"/>
       <c r="G161" s="18"/>
@@ -8179,7 +8179,7 @@
       <c r="A162" s="17"/>
       <c r="B162" s="18"/>
       <c r="C162" s="33"/>
-      <c r="D162" s="58"/>
+      <c r="D162" s="57"/>
       <c r="E162" s="19"/>
       <c r="F162" s="20"/>
       <c r="G162" s="18"/>
@@ -8207,7 +8207,7 @@
       <c r="A163" s="17"/>
       <c r="B163" s="18"/>
       <c r="C163" s="33"/>
-      <c r="D163" s="58"/>
+      <c r="D163" s="57"/>
       <c r="E163" s="19"/>
       <c r="F163" s="20"/>
       <c r="G163" s="18"/>
@@ -8235,7 +8235,7 @@
       <c r="A164" s="17"/>
       <c r="B164" s="18"/>
       <c r="C164" s="33"/>
-      <c r="D164" s="58"/>
+      <c r="D164" s="57"/>
       <c r="E164" s="19"/>
       <c r="F164" s="20"/>
       <c r="G164" s="18"/>
@@ -8263,7 +8263,7 @@
       <c r="A165" s="17"/>
       <c r="B165" s="18"/>
       <c r="C165" s="33"/>
-      <c r="D165" s="58"/>
+      <c r="D165" s="57"/>
       <c r="E165" s="19"/>
       <c r="F165" s="20"/>
       <c r="G165" s="18"/>
@@ -8291,7 +8291,7 @@
       <c r="A166" s="17"/>
       <c r="B166" s="18"/>
       <c r="C166" s="33"/>
-      <c r="D166" s="58"/>
+      <c r="D166" s="57"/>
       <c r="E166" s="19"/>
       <c r="F166" s="20"/>
       <c r="G166" s="18"/>
@@ -8319,7 +8319,7 @@
       <c r="A167" s="17"/>
       <c r="B167" s="18"/>
       <c r="C167" s="33"/>
-      <c r="D167" s="58"/>
+      <c r="D167" s="57"/>
       <c r="E167" s="19"/>
       <c r="F167" s="20"/>
       <c r="G167" s="18"/>
@@ -8347,7 +8347,7 @@
       <c r="A168" s="17"/>
       <c r="B168" s="18"/>
       <c r="C168" s="33"/>
-      <c r="D168" s="58"/>
+      <c r="D168" s="57"/>
       <c r="E168" s="19"/>
       <c r="F168" s="20"/>
       <c r="G168" s="18"/>
@@ -8375,7 +8375,7 @@
       <c r="A169" s="17"/>
       <c r="B169" s="18"/>
       <c r="C169" s="33"/>
-      <c r="D169" s="58"/>
+      <c r="D169" s="57"/>
       <c r="E169" s="19"/>
       <c r="F169" s="20"/>
       <c r="G169" s="18"/>
@@ -8403,7 +8403,7 @@
       <c r="A170" s="17"/>
       <c r="B170" s="18"/>
       <c r="C170" s="33"/>
-      <c r="D170" s="58"/>
+      <c r="D170" s="57"/>
       <c r="E170" s="19"/>
       <c r="F170" s="20"/>
       <c r="G170" s="18"/>
@@ -8431,7 +8431,7 @@
       <c r="A171" s="17"/>
       <c r="B171" s="18"/>
       <c r="C171" s="33"/>
-      <c r="D171" s="58"/>
+      <c r="D171" s="57"/>
       <c r="E171" s="19"/>
       <c r="F171" s="20"/>
       <c r="G171" s="18"/>
@@ -8459,7 +8459,7 @@
       <c r="A172" s="17"/>
       <c r="B172" s="18"/>
       <c r="C172" s="33"/>
-      <c r="D172" s="58"/>
+      <c r="D172" s="57"/>
       <c r="E172" s="19"/>
       <c r="F172" s="20"/>
       <c r="G172" s="18"/>
@@ -8487,7 +8487,7 @@
       <c r="A173" s="17"/>
       <c r="B173" s="18"/>
       <c r="C173" s="33"/>
-      <c r="D173" s="58"/>
+      <c r="D173" s="57"/>
       <c r="E173" s="19"/>
       <c r="F173" s="20"/>
       <c r="G173" s="18"/>
@@ -8515,7 +8515,7 @@
       <c r="A174" s="17"/>
       <c r="B174" s="18"/>
       <c r="C174" s="33"/>
-      <c r="D174" s="58"/>
+      <c r="D174" s="57"/>
       <c r="E174" s="19"/>
       <c r="F174" s="20"/>
       <c r="G174" s="18"/>
@@ -8543,7 +8543,7 @@
       <c r="A175" s="17"/>
       <c r="B175" s="18"/>
       <c r="C175" s="33"/>
-      <c r="D175" s="58"/>
+      <c r="D175" s="57"/>
       <c r="E175" s="19"/>
       <c r="F175" s="20"/>
       <c r="G175" s="18"/>
@@ -8571,7 +8571,7 @@
       <c r="A176" s="17"/>
       <c r="B176" s="18"/>
       <c r="C176" s="33"/>
-      <c r="D176" s="58"/>
+      <c r="D176" s="57"/>
       <c r="E176" s="19"/>
       <c r="F176" s="20"/>
       <c r="G176" s="18"/>
@@ -8599,7 +8599,7 @@
       <c r="A177" s="17"/>
       <c r="B177" s="18"/>
       <c r="C177" s="33"/>
-      <c r="D177" s="58"/>
+      <c r="D177" s="57"/>
       <c r="E177" s="19"/>
       <c r="F177" s="20"/>
       <c r="G177" s="18"/>
@@ -8627,7 +8627,7 @@
       <c r="A178" s="17"/>
       <c r="B178" s="18"/>
       <c r="C178" s="33"/>
-      <c r="D178" s="58"/>
+      <c r="D178" s="57"/>
       <c r="E178" s="19"/>
       <c r="F178" s="20"/>
       <c r="G178" s="18"/>
@@ -8655,7 +8655,7 @@
       <c r="A179" s="17"/>
       <c r="B179" s="18"/>
       <c r="C179" s="33"/>
-      <c r="D179" s="58"/>
+      <c r="D179" s="57"/>
       <c r="E179" s="19"/>
       <c r="F179" s="20"/>
       <c r="G179" s="18"/>
@@ -8683,7 +8683,7 @@
       <c r="A180" s="17"/>
       <c r="B180" s="18"/>
       <c r="C180" s="33"/>
-      <c r="D180" s="58"/>
+      <c r="D180" s="57"/>
       <c r="E180" s="19"/>
       <c r="F180" s="20"/>
       <c r="G180" s="18"/>
@@ -8711,7 +8711,7 @@
       <c r="A181" s="17"/>
       <c r="B181" s="18"/>
       <c r="C181" s="33"/>
-      <c r="D181" s="58"/>
+      <c r="D181" s="57"/>
       <c r="E181" s="19"/>
       <c r="F181" s="20"/>
       <c r="G181" s="18"/>
@@ -8739,7 +8739,7 @@
       <c r="A182" s="17"/>
       <c r="B182" s="18"/>
       <c r="C182" s="33"/>
-      <c r="D182" s="58"/>
+      <c r="D182" s="57"/>
       <c r="E182" s="19"/>
       <c r="F182" s="20"/>
       <c r="G182" s="18"/>
@@ -8767,7 +8767,7 @@
       <c r="A183" s="17"/>
       <c r="B183" s="18"/>
       <c r="C183" s="33"/>
-      <c r="D183" s="58"/>
+      <c r="D183" s="57"/>
       <c r="E183" s="19"/>
       <c r="F183" s="20"/>
       <c r="G183" s="18"/>
@@ -8795,7 +8795,7 @@
       <c r="A184" s="17"/>
       <c r="B184" s="18"/>
       <c r="C184" s="33"/>
-      <c r="D184" s="58"/>
+      <c r="D184" s="57"/>
       <c r="E184" s="19"/>
       <c r="F184" s="20"/>
       <c r="G184" s="18"/>
@@ -8823,7 +8823,7 @@
       <c r="A185" s="17"/>
       <c r="B185" s="18"/>
       <c r="C185" s="33"/>
-      <c r="D185" s="58"/>
+      <c r="D185" s="57"/>
       <c r="E185" s="19"/>
       <c r="F185" s="20"/>
       <c r="G185" s="18"/>
@@ -8851,7 +8851,7 @@
       <c r="A186" s="17"/>
       <c r="B186" s="18"/>
       <c r="C186" s="33"/>
-      <c r="D186" s="58"/>
+      <c r="D186" s="57"/>
       <c r="E186" s="19"/>
       <c r="F186" s="20"/>
       <c r="G186" s="18"/>
@@ -8879,7 +8879,7 @@
       <c r="A187" s="17"/>
       <c r="B187" s="18"/>
       <c r="C187" s="33"/>
-      <c r="D187" s="58"/>
+      <c r="D187" s="57"/>
       <c r="E187" s="19"/>
       <c r="F187" s="20"/>
       <c r="G187" s="18"/>
@@ -8907,7 +8907,7 @@
       <c r="A188" s="17"/>
       <c r="B188" s="18"/>
       <c r="C188" s="33"/>
-      <c r="D188" s="58"/>
+      <c r="D188" s="57"/>
       <c r="E188" s="19"/>
       <c r="F188" s="20"/>
       <c r="G188" s="18"/>
@@ -8935,7 +8935,7 @@
       <c r="A189" s="17"/>
       <c r="B189" s="18"/>
       <c r="C189" s="33"/>
-      <c r="D189" s="58"/>
+      <c r="D189" s="57"/>
       <c r="E189" s="19"/>
       <c r="F189" s="20"/>
       <c r="G189" s="18"/>
@@ -8963,7 +8963,7 @@
       <c r="A190" s="17"/>
       <c r="B190" s="18"/>
       <c r="C190" s="33"/>
-      <c r="D190" s="58"/>
+      <c r="D190" s="57"/>
       <c r="E190" s="19"/>
       <c r="F190" s="20"/>
       <c r="G190" s="18"/>
@@ -8991,7 +8991,7 @@
       <c r="A191" s="17"/>
       <c r="B191" s="18"/>
       <c r="C191" s="33"/>
-      <c r="D191" s="58"/>
+      <c r="D191" s="57"/>
       <c r="E191" s="19"/>
       <c r="F191" s="20"/>
       <c r="G191" s="18"/>
@@ -9019,7 +9019,7 @@
       <c r="A192" s="17"/>
       <c r="B192" s="18"/>
       <c r="C192" s="33"/>
-      <c r="D192" s="58"/>
+      <c r="D192" s="57"/>
       <c r="E192" s="19"/>
       <c r="F192" s="20"/>
       <c r="G192" s="18"/>
@@ -9047,7 +9047,7 @@
       <c r="A193" s="17"/>
       <c r="B193" s="18"/>
       <c r="C193" s="33"/>
-      <c r="D193" s="58"/>
+      <c r="D193" s="57"/>
       <c r="E193" s="19"/>
       <c r="F193" s="20"/>
       <c r="G193" s="18"/>
@@ -9075,7 +9075,7 @@
       <c r="A194" s="17"/>
       <c r="B194" s="18"/>
       <c r="C194" s="33"/>
-      <c r="D194" s="58"/>
+      <c r="D194" s="57"/>
       <c r="E194" s="19"/>
       <c r="F194" s="20"/>
       <c r="G194" s="18"/>
@@ -9103,7 +9103,7 @@
       <c r="A195" s="17"/>
       <c r="B195" s="18"/>
       <c r="C195" s="33"/>
-      <c r="D195" s="58"/>
+      <c r="D195" s="57"/>
       <c r="E195" s="19"/>
       <c r="F195" s="20"/>
       <c r="G195" s="18"/>
@@ -9131,7 +9131,7 @@
       <c r="A196" s="17"/>
       <c r="B196" s="18"/>
       <c r="C196" s="33"/>
-      <c r="D196" s="58"/>
+      <c r="D196" s="57"/>
       <c r="E196" s="19"/>
       <c r="F196" s="20"/>
       <c r="G196" s="18"/>
@@ -9159,7 +9159,7 @@
       <c r="A197" s="17"/>
       <c r="B197" s="18"/>
       <c r="C197" s="33"/>
-      <c r="D197" s="58"/>
+      <c r="D197" s="57"/>
       <c r="E197" s="19"/>
       <c r="F197" s="20"/>
       <c r="G197" s="18"/>
@@ -9187,7 +9187,7 @@
       <c r="A198" s="17"/>
       <c r="B198" s="18"/>
       <c r="C198" s="33"/>
-      <c r="D198" s="58"/>
+      <c r="D198" s="57"/>
       <c r="E198" s="19"/>
       <c r="F198" s="20"/>
       <c r="G198" s="18"/>
@@ -9215,7 +9215,7 @@
       <c r="A199" s="17"/>
       <c r="B199" s="18"/>
       <c r="C199" s="33"/>
-      <c r="D199" s="58"/>
+      <c r="D199" s="57"/>
       <c r="E199" s="19"/>
       <c r="F199" s="20"/>
       <c r="G199" s="18"/>
@@ -9243,7 +9243,7 @@
       <c r="A200" s="17"/>
       <c r="B200" s="18"/>
       <c r="C200" s="33"/>
-      <c r="D200" s="58"/>
+      <c r="D200" s="57"/>
       <c r="E200" s="19"/>
       <c r="F200" s="20"/>
       <c r="G200" s="18"/>
@@ -9271,7 +9271,7 @@
       <c r="A201" s="17"/>
       <c r="B201" s="18"/>
       <c r="C201" s="33"/>
-      <c r="D201" s="58"/>
+      <c r="D201" s="57"/>
       <c r="E201" s="19"/>
       <c r="F201" s="20"/>
       <c r="G201" s="18"/>
@@ -9299,7 +9299,7 @@
       <c r="A202" s="17"/>
       <c r="B202" s="18"/>
       <c r="C202" s="33"/>
-      <c r="D202" s="58"/>
+      <c r="D202" s="57"/>
       <c r="E202" s="19"/>
       <c r="F202" s="20"/>
       <c r="G202" s="18"/>
@@ -9327,7 +9327,7 @@
       <c r="A203" s="17"/>
       <c r="B203" s="18"/>
       <c r="C203" s="33"/>
-      <c r="D203" s="58"/>
+      <c r="D203" s="57"/>
       <c r="E203" s="19"/>
       <c r="F203" s="20"/>
       <c r="G203" s="18"/>
@@ -9355,7 +9355,7 @@
       <c r="A204" s="17"/>
       <c r="B204" s="18"/>
       <c r="C204" s="33"/>
-      <c r="D204" s="58"/>
+      <c r="D204" s="57"/>
       <c r="E204" s="19"/>
       <c r="F204" s="20"/>
       <c r="G204" s="18"/>
@@ -9383,7 +9383,7 @@
       <c r="A205" s="17"/>
       <c r="B205" s="18"/>
       <c r="C205" s="33"/>
-      <c r="D205" s="58"/>
+      <c r="D205" s="57"/>
       <c r="E205" s="19"/>
       <c r="F205" s="20"/>
       <c r="G205" s="18"/>
@@ -9411,7 +9411,7 @@
       <c r="A206" s="17"/>
       <c r="B206" s="18"/>
       <c r="C206" s="33"/>
-      <c r="D206" s="58"/>
+      <c r="D206" s="57"/>
       <c r="E206" s="19"/>
       <c r="F206" s="20"/>
       <c r="G206" s="18"/>
@@ -9439,7 +9439,7 @@
       <c r="A207" s="17"/>
       <c r="B207" s="18"/>
       <c r="C207" s="33"/>
-      <c r="D207" s="58"/>
+      <c r="D207" s="57"/>
       <c r="E207" s="19"/>
       <c r="F207" s="20"/>
       <c r="G207" s="18"/>
@@ -9467,7 +9467,7 @@
       <c r="A208" s="17"/>
       <c r="B208" s="18"/>
       <c r="C208" s="33"/>
-      <c r="D208" s="58"/>
+      <c r="D208" s="57"/>
       <c r="E208" s="19"/>
       <c r="F208" s="20"/>
       <c r="G208" s="18"/>
@@ -9495,7 +9495,7 @@
       <c r="A209" s="17"/>
       <c r="B209" s="18"/>
       <c r="C209" s="33"/>
-      <c r="D209" s="58"/>
+      <c r="D209" s="57"/>
       <c r="E209" s="19"/>
       <c r="F209" s="20"/>
       <c r="G209" s="18"/>
@@ -9523,7 +9523,7 @@
       <c r="A210" s="17"/>
       <c r="B210" s="18"/>
       <c r="C210" s="33"/>
-      <c r="D210" s="58"/>
+      <c r="D210" s="57"/>
       <c r="E210" s="19"/>
       <c r="F210" s="20"/>
       <c r="G210" s="18"/>
@@ -9551,7 +9551,7 @@
       <c r="A211" s="17"/>
       <c r="B211" s="18"/>
       <c r="C211" s="33"/>
-      <c r="D211" s="58"/>
+      <c r="D211" s="57"/>
       <c r="E211" s="19"/>
       <c r="F211" s="20"/>
       <c r="G211" s="18"/>
@@ -9579,7 +9579,7 @@
       <c r="A212" s="17"/>
       <c r="B212" s="18"/>
       <c r="C212" s="33"/>
-      <c r="D212" s="58"/>
+      <c r="D212" s="57"/>
       <c r="E212" s="19"/>
       <c r="F212" s="20"/>
       <c r="G212" s="18"/>
@@ -9607,7 +9607,7 @@
       <c r="A213" s="17"/>
       <c r="B213" s="18"/>
       <c r="C213" s="33"/>
-      <c r="D213" s="58"/>
+      <c r="D213" s="57"/>
       <c r="E213" s="19"/>
       <c r="F213" s="20"/>
       <c r="G213" s="18"/>
@@ -9635,7 +9635,7 @@
       <c r="A214" s="17"/>
       <c r="B214" s="18"/>
       <c r="C214" s="33"/>
-      <c r="D214" s="58"/>
+      <c r="D214" s="57"/>
       <c r="E214" s="19"/>
       <c r="F214" s="20"/>
       <c r="G214" s="18"/>
@@ -9663,7 +9663,7 @@
       <c r="A215" s="17"/>
       <c r="B215" s="18"/>
       <c r="C215" s="33"/>
-      <c r="D215" s="58"/>
+      <c r="D215" s="57"/>
       <c r="E215" s="19"/>
       <c r="F215" s="20"/>
       <c r="G215" s="18"/>
@@ -9691,7 +9691,7 @@
       <c r="A216" s="17"/>
       <c r="B216" s="18"/>
       <c r="C216" s="33"/>
-      <c r="D216" s="58"/>
+      <c r="D216" s="57"/>
       <c r="E216" s="19"/>
       <c r="F216" s="20"/>
       <c r="G216" s="18"/>
@@ -9719,7 +9719,7 @@
       <c r="A217" s="17"/>
       <c r="B217" s="18"/>
       <c r="C217" s="33"/>
-      <c r="D217" s="58"/>
+      <c r="D217" s="57"/>
       <c r="E217" s="19"/>
       <c r="F217" s="20"/>
       <c r="G217" s="18"/>
@@ -9747,7 +9747,7 @@
       <c r="A218" s="17"/>
       <c r="B218" s="18"/>
       <c r="C218" s="33"/>
-      <c r="D218" s="58"/>
+      <c r="D218" s="57"/>
       <c r="E218" s="19"/>
       <c r="F218" s="20"/>
       <c r="G218" s="18"/>
@@ -9775,7 +9775,7 @@
       <c r="A219" s="17"/>
       <c r="B219" s="18"/>
       <c r="C219" s="33"/>
-      <c r="D219" s="58"/>
+      <c r="D219" s="57"/>
       <c r="E219" s="19"/>
       <c r="F219" s="20"/>
       <c r="G219" s="18"/>
@@ -9803,7 +9803,7 @@
       <c r="A220" s="17"/>
       <c r="B220" s="18"/>
       <c r="C220" s="33"/>
-      <c r="D220" s="58"/>
+      <c r="D220" s="57"/>
       <c r="E220" s="19"/>
       <c r="F220" s="20"/>
       <c r="G220" s="18"/>
@@ -9831,7 +9831,7 @@
       <c r="A221" s="17"/>
       <c r="B221" s="18"/>
       <c r="C221" s="33"/>
-      <c r="D221" s="58"/>
+      <c r="D221" s="57"/>
       <c r="E221" s="19"/>
       <c r="F221" s="20"/>
       <c r="G221" s="18"/>
@@ -9859,7 +9859,7 @@
       <c r="A222" s="17"/>
       <c r="B222" s="18"/>
       <c r="C222" s="33"/>
-      <c r="D222" s="58"/>
+      <c r="D222" s="57"/>
       <c r="E222" s="19"/>
       <c r="F222" s="20"/>
       <c r="G222" s="18"/>
@@ -9887,7 +9887,7 @@
       <c r="A223" s="17"/>
       <c r="B223" s="18"/>
       <c r="C223" s="33"/>
-      <c r="D223" s="58"/>
+      <c r="D223" s="57"/>
       <c r="E223" s="19"/>
       <c r="F223" s="20"/>
       <c r="G223" s="18"/>
@@ -9915,7 +9915,7 @@
       <c r="A224" s="17"/>
       <c r="B224" s="18"/>
       <c r="C224" s="33"/>
-      <c r="D224" s="58"/>
+      <c r="D224" s="57"/>
       <c r="E224" s="19"/>
       <c r="F224" s="20"/>
       <c r="G224" s="18"/>
@@ -9943,7 +9943,7 @@
       <c r="A225" s="17"/>
       <c r="B225" s="18"/>
       <c r="C225" s="33"/>
-      <c r="D225" s="58"/>
+      <c r="D225" s="57"/>
       <c r="E225" s="19"/>
       <c r="F225" s="20"/>
       <c r="G225" s="18"/>
@@ -9971,7 +9971,7 @@
       <c r="A226" s="17"/>
       <c r="B226" s="18"/>
       <c r="C226" s="33"/>
-      <c r="D226" s="58"/>
+      <c r="D226" s="57"/>
       <c r="E226" s="19"/>
       <c r="F226" s="20"/>
       <c r="G226" s="18"/>
@@ -9999,7 +9999,7 @@
       <c r="A227" s="17"/>
       <c r="B227" s="18"/>
       <c r="C227" s="33"/>
-      <c r="D227" s="58"/>
+      <c r="D227" s="57"/>
       <c r="E227" s="19"/>
       <c r="F227" s="20"/>
       <c r="G227" s="18"/>
@@ -10027,7 +10027,7 @@
       <c r="A228" s="17"/>
       <c r="B228" s="18"/>
       <c r="C228" s="33"/>
-      <c r="D228" s="58"/>
+      <c r="D228" s="57"/>
       <c r="E228" s="19"/>
       <c r="F228" s="20"/>
       <c r="G228" s="18"/>
@@ -10055,7 +10055,7 @@
       <c r="A229" s="17"/>
       <c r="B229" s="18"/>
       <c r="C229" s="33"/>
-      <c r="D229" s="58"/>
+      <c r="D229" s="57"/>
       <c r="E229" s="19"/>
       <c r="F229" s="20"/>
       <c r="G229" s="18"/>
@@ -10083,7 +10083,7 @@
       <c r="A230" s="17"/>
       <c r="B230" s="18"/>
       <c r="C230" s="33"/>
-      <c r="D230" s="58"/>
+      <c r="D230" s="57"/>
       <c r="E230" s="19"/>
       <c r="F230" s="20"/>
       <c r="G230" s="18"/>
@@ -10111,7 +10111,7 @@
       <c r="A231" s="17"/>
       <c r="B231" s="18"/>
       <c r="C231" s="33"/>
-      <c r="D231" s="58"/>
+      <c r="D231" s="57"/>
       <c r="E231" s="19"/>
       <c r="F231" s="20"/>
       <c r="G231" s="18"/>
@@ -10139,7 +10139,7 @@
       <c r="A232" s="17"/>
       <c r="B232" s="18"/>
       <c r="C232" s="33"/>
-      <c r="D232" s="58"/>
+      <c r="D232" s="57"/>
       <c r="E232" s="19"/>
       <c r="F232" s="20"/>
       <c r="G232" s="18"/>
@@ -10167,7 +10167,7 @@
       <c r="A233" s="17"/>
       <c r="B233" s="18"/>
       <c r="C233" s="33"/>
-      <c r="D233" s="58"/>
+      <c r="D233" s="57"/>
       <c r="E233" s="19"/>
       <c r="F233" s="20"/>
       <c r="G233" s="18"/>
@@ -10195,7 +10195,7 @@
       <c r="A234" s="17"/>
       <c r="B234" s="18"/>
       <c r="C234" s="33"/>
-      <c r="D234" s="58"/>
+      <c r="D234" s="57"/>
       <c r="E234" s="19"/>
       <c r="F234" s="20"/>
       <c r="G234" s="18"/>
@@ -10223,7 +10223,7 @@
       <c r="A235" s="17"/>
       <c r="B235" s="18"/>
       <c r="C235" s="33"/>
-      <c r="D235" s="58"/>
+      <c r="D235" s="57"/>
       <c r="E235" s="19"/>
       <c r="F235" s="20"/>
       <c r="G235" s="18"/>
@@ -10251,7 +10251,7 @@
       <c r="A236" s="17"/>
       <c r="B236" s="18"/>
       <c r="C236" s="33"/>
-      <c r="D236" s="58"/>
+      <c r="D236" s="57"/>
       <c r="E236" s="19"/>
       <c r="F236" s="20"/>
       <c r="G236" s="18"/>
@@ -10279,7 +10279,7 @@
       <c r="A237" s="17"/>
       <c r="B237" s="18"/>
       <c r="C237" s="33"/>
-      <c r="D237" s="58"/>
+      <c r="D237" s="57"/>
       <c r="E237" s="19"/>
       <c r="F237" s="20"/>
       <c r="G237" s="18"/>
@@ -10307,7 +10307,7 @@
       <c r="A238" s="17"/>
       <c r="B238" s="18"/>
       <c r="C238" s="33"/>
-      <c r="D238" s="58"/>
+      <c r="D238" s="57"/>
       <c r="E238" s="19"/>
       <c r="F238" s="20"/>
       <c r="G238" s="18"/>
@@ -10335,7 +10335,7 @@
       <c r="A239" s="17"/>
       <c r="B239" s="18"/>
       <c r="C239" s="33"/>
-      <c r="D239" s="58"/>
+      <c r="D239" s="57"/>
       <c r="E239" s="19"/>
       <c r="F239" s="20"/>
       <c r="G239" s="18"/>
@@ -10363,7 +10363,7 @@
       <c r="A240" s="17"/>
       <c r="B240" s="18"/>
       <c r="C240" s="33"/>
-      <c r="D240" s="58"/>
+      <c r="D240" s="57"/>
       <c r="E240" s="19"/>
       <c r="F240" s="20"/>
       <c r="G240" s="18"/>
@@ -10391,7 +10391,7 @@
       <c r="A241" s="17"/>
       <c r="B241" s="18"/>
       <c r="C241" s="33"/>
-      <c r="D241" s="58"/>
+      <c r="D241" s="57"/>
       <c r="E241" s="19"/>
       <c r="F241" s="20"/>
       <c r="G241" s="18"/>
@@ -10419,7 +10419,7 @@
       <c r="A242" s="17"/>
       <c r="B242" s="18"/>
       <c r="C242" s="33"/>
-      <c r="D242" s="58"/>
+      <c r="D242" s="57"/>
       <c r="E242" s="19"/>
       <c r="F242" s="20"/>
       <c r="G242" s="18"/>
@@ -10447,7 +10447,7 @@
       <c r="A243" s="17"/>
       <c r="B243" s="18"/>
       <c r="C243" s="33"/>
-      <c r="D243" s="58"/>
+      <c r="D243" s="57"/>
       <c r="E243" s="19"/>
       <c r="F243" s="20"/>
       <c r="G243" s="18"/>
@@ -10475,7 +10475,7 @@
       <c r="A244" s="17"/>
       <c r="B244" s="18"/>
       <c r="C244" s="33"/>
-      <c r="D244" s="58"/>
+      <c r="D244" s="57"/>
       <c r="E244" s="19"/>
       <c r="F244" s="20"/>
       <c r="G244" s="18"/>
@@ -10503,7 +10503,7 @@
       <c r="A245" s="17"/>
       <c r="B245" s="18"/>
       <c r="C245" s="33"/>
-      <c r="D245" s="58"/>
+      <c r="D245" s="57"/>
       <c r="E245" s="19"/>
       <c r="F245" s="20"/>
       <c r="G245" s="18"/>
@@ -10531,7 +10531,7 @@
       <c r="A246" s="17"/>
       <c r="B246" s="18"/>
       <c r="C246" s="33"/>
-      <c r="D246" s="58"/>
+      <c r="D246" s="57"/>
       <c r="E246" s="19"/>
       <c r="F246" s="20"/>
       <c r="G246" s="18"/>
@@ -10559,7 +10559,7 @@
       <c r="A247" s="17"/>
       <c r="B247" s="18"/>
       <c r="C247" s="33"/>
-      <c r="D247" s="58"/>
+      <c r="D247" s="57"/>
       <c r="E247" s="19"/>
       <c r="F247" s="20"/>
       <c r="G247" s="18"/>
@@ -10587,7 +10587,7 @@
       <c r="A248" s="17"/>
       <c r="B248" s="18"/>
       <c r="C248" s="33"/>
-      <c r="D248" s="58"/>
+      <c r="D248" s="57"/>
       <c r="E248" s="19"/>
       <c r="F248" s="20"/>
       <c r="G248" s="18"/>
@@ -10615,7 +10615,7 @@
       <c r="A249" s="17"/>
       <c r="B249" s="18"/>
       <c r="C249" s="33"/>
-      <c r="D249" s="58"/>
+      <c r="D249" s="57"/>
       <c r="E249" s="19"/>
       <c r="F249" s="20"/>
       <c r="G249" s="18"/>
@@ -10643,7 +10643,7 @@
       <c r="A250" s="17"/>
       <c r="B250" s="18"/>
       <c r="C250" s="33"/>
-      <c r="D250" s="58"/>
+      <c r="D250" s="57"/>
       <c r="E250" s="19"/>
       <c r="F250" s="20"/>
       <c r="G250" s="18"/>
@@ -10671,7 +10671,7 @@
       <c r="A251" s="17"/>
       <c r="B251" s="18"/>
       <c r="C251" s="33"/>
-      <c r="D251" s="58"/>
+      <c r="D251" s="57"/>
       <c r="E251" s="19"/>
       <c r="F251" s="20"/>
       <c r="G251" s="18"/>
@@ -10699,7 +10699,7 @@
       <c r="A252" s="17"/>
       <c r="B252" s="18"/>
       <c r="C252" s="33"/>
-      <c r="D252" s="58"/>
+      <c r="D252" s="57"/>
       <c r="E252" s="19"/>
       <c r="F252" s="20"/>
       <c r="G252" s="18"/>
@@ -10727,7 +10727,7 @@
       <c r="A253" s="17"/>
       <c r="B253" s="18"/>
       <c r="C253" s="33"/>
-      <c r="D253" s="58"/>
+      <c r="D253" s="57"/>
       <c r="E253" s="19"/>
       <c r="F253" s="20"/>
       <c r="G253" s="18"/>
@@ -10755,7 +10755,7 @@
       <c r="A254" s="17"/>
       <c r="B254" s="18"/>
       <c r="C254" s="33"/>
-      <c r="D254" s="58"/>
+      <c r="D254" s="57"/>
       <c r="E254" s="19"/>
       <c r="F254" s="20"/>
       <c r="G254" s="18"/>
@@ -10783,7 +10783,7 @@
       <c r="A255" s="17"/>
       <c r="B255" s="18"/>
       <c r="C255" s="33"/>
-      <c r="D255" s="58"/>
+      <c r="D255" s="57"/>
       <c r="E255" s="19"/>
       <c r="F255" s="20"/>
       <c r="G255" s="18"/>
@@ -10811,7 +10811,7 @@
       <c r="A256" s="17"/>
       <c r="B256" s="18"/>
       <c r="C256" s="33"/>
-      <c r="D256" s="58"/>
+      <c r="D256" s="57"/>
       <c r="E256" s="19"/>
       <c r="F256" s="20"/>
       <c r="G256" s="18"/>
@@ -10839,7 +10839,7 @@
       <c r="A257" s="17"/>
       <c r="B257" s="18"/>
       <c r="C257" s="33"/>
-      <c r="D257" s="58"/>
+      <c r="D257" s="57"/>
       <c r="E257" s="19"/>
       <c r="F257" s="20"/>
       <c r="G257" s="18"/>
@@ -10867,7 +10867,7 @@
       <c r="A258" s="17"/>
       <c r="B258" s="18"/>
       <c r="C258" s="33"/>
-      <c r="D258" s="58"/>
+      <c r="D258" s="57"/>
       <c r="E258" s="19"/>
       <c r="F258" s="20"/>
       <c r="G258" s="18"/>
@@ -10895,7 +10895,7 @@
       <c r="A259" s="17"/>
       <c r="B259" s="18"/>
       <c r="C259" s="33"/>
-      <c r="D259" s="58"/>
+      <c r="D259" s="57"/>
       <c r="E259" s="19"/>
       <c r="F259" s="20"/>
       <c r="G259" s="18"/>
@@ -10923,7 +10923,7 @@
       <c r="A260" s="17"/>
       <c r="B260" s="18"/>
       <c r="C260" s="33"/>
-      <c r="D260" s="58"/>
+      <c r="D260" s="57"/>
       <c r="E260" s="19"/>
       <c r="F260" s="20"/>
       <c r="G260" s="18"/>
@@ -10951,7 +10951,7 @@
       <c r="A261" s="17"/>
       <c r="B261" s="18"/>
       <c r="C261" s="33"/>
-      <c r="D261" s="58"/>
+      <c r="D261" s="57"/>
       <c r="E261" s="19"/>
       <c r="F261" s="20"/>
       <c r="G261" s="18"/>
@@ -10979,7 +10979,7 @@
       <c r="A262" s="17"/>
       <c r="B262" s="18"/>
       <c r="C262" s="33"/>
-      <c r="D262" s="58"/>
+      <c r="D262" s="57"/>
       <c r="E262" s="19"/>
       <c r="F262" s="20"/>
       <c r="G262" s="18"/>
@@ -11007,7 +11007,7 @@
       <c r="A263" s="17"/>
       <c r="B263" s="18"/>
       <c r="C263" s="33"/>
-      <c r="D263" s="58"/>
+      <c r="D263" s="57"/>
       <c r="E263" s="19"/>
       <c r="F263" s="20"/>
       <c r="G263" s="18"/>
@@ -11035,7 +11035,7 @@
       <c r="A264" s="17"/>
       <c r="B264" s="18"/>
       <c r="C264" s="33"/>
-      <c r="D264" s="58"/>
+      <c r="D264" s="57"/>
       <c r="E264" s="19"/>
       <c r="F264" s="20"/>
       <c r="G264" s="18"/>
@@ -11063,7 +11063,7 @@
       <c r="A265" s="17"/>
       <c r="B265" s="18"/>
       <c r="C265" s="33"/>
-      <c r="D265" s="58"/>
+      <c r="D265" s="57"/>
       <c r="E265" s="19"/>
       <c r="F265" s="20"/>
       <c r="G265" s="18"/>
@@ -11091,7 +11091,7 @@
       <c r="A266" s="17"/>
       <c r="B266" s="18"/>
       <c r="C266" s="33"/>
-      <c r="D266" s="58"/>
+      <c r="D266" s="57"/>
       <c r="E266" s="19"/>
       <c r="F266" s="20"/>
       <c r="G266" s="18"/>
@@ -11119,7 +11119,7 @@
       <c r="A267" s="17"/>
       <c r="B267" s="18"/>
       <c r="C267" s="33"/>
-      <c r="D267" s="58"/>
+      <c r="D267" s="57"/>
       <c r="E267" s="19"/>
       <c r="F267" s="20"/>
       <c r="G267" s="18"/>
@@ -11147,7 +11147,7 @@
       <c r="A268" s="17"/>
       <c r="B268" s="18"/>
       <c r="C268" s="33"/>
-      <c r="D268" s="58"/>
+      <c r="D268" s="57"/>
       <c r="E268" s="19"/>
       <c r="F268" s="20"/>
       <c r="G268" s="18"/>
@@ -11175,7 +11175,7 @@
       <c r="A269" s="17"/>
       <c r="B269" s="18"/>
       <c r="C269" s="33"/>
-      <c r="D269" s="58"/>
+      <c r="D269" s="57"/>
       <c r="E269" s="19"/>
       <c r="F269" s="20"/>
       <c r="G269" s="18"/>
@@ -11203,7 +11203,7 @@
       <c r="A270" s="17"/>
       <c r="B270" s="18"/>
       <c r="C270" s="33"/>
-      <c r="D270" s="58"/>
+      <c r="D270" s="57"/>
       <c r="E270" s="19"/>
       <c r="F270" s="20"/>
       <c r="G270" s="18"/>
@@ -11231,7 +11231,7 @@
       <c r="A271" s="17"/>
       <c r="B271" s="18"/>
       <c r="C271" s="33"/>
-      <c r="D271" s="58"/>
+      <c r="D271" s="57"/>
       <c r="E271" s="19"/>
       <c r="F271" s="20"/>
       <c r="G271" s="18"/>
@@ -11259,7 +11259,7 @@
       <c r="A272" s="17"/>
       <c r="B272" s="18"/>
       <c r="C272" s="33"/>
-      <c r="D272" s="58"/>
+      <c r="D272" s="57"/>
       <c r="E272" s="19"/>
       <c r="F272" s="20"/>
       <c r="G272" s="18"/>
@@ -11287,7 +11287,7 @@
       <c r="A273" s="17"/>
       <c r="B273" s="18"/>
       <c r="C273" s="33"/>
-      <c r="D273" s="58"/>
+      <c r="D273" s="57"/>
       <c r="E273" s="19"/>
       <c r="F273" s="20"/>
       <c r="G273" s="18"/>
@@ -11315,7 +11315,7 @@
       <c r="A274" s="17"/>
       <c r="B274" s="18"/>
       <c r="C274" s="33"/>
-      <c r="D274" s="58"/>
+      <c r="D274" s="57"/>
       <c r="E274" s="19"/>
       <c r="F274" s="20"/>
       <c r="G274" s="18"/>
@@ -11343,7 +11343,7 @@
       <c r="A275" s="17"/>
       <c r="B275" s="18"/>
       <c r="C275" s="33"/>
-      <c r="D275" s="58"/>
+      <c r="D275" s="57"/>
       <c r="E275" s="19"/>
       <c r="F275" s="20"/>
       <c r="G275" s="18"/>
@@ -11371,7 +11371,7 @@
       <c r="A276" s="17"/>
       <c r="B276" s="18"/>
       <c r="C276" s="33"/>
-      <c r="D276" s="58"/>
+      <c r="D276" s="57"/>
       <c r="E276" s="19"/>
       <c r="F276" s="20"/>
       <c r="G276" s="18"/>
@@ -11399,7 +11399,7 @@
       <c r="A277" s="17"/>
       <c r="B277" s="18"/>
       <c r="C277" s="33"/>
-      <c r="D277" s="58"/>
+      <c r="D277" s="57"/>
       <c r="E277" s="19"/>
       <c r="F277" s="20"/>
       <c r="G277" s="18"/>
@@ -11427,7 +11427,7 @@
       <c r="A278" s="17"/>
       <c r="B278" s="18"/>
       <c r="C278" s="33"/>
-      <c r="D278" s="58"/>
+      <c r="D278" s="57"/>
       <c r="E278" s="19"/>
       <c r="F278" s="20"/>
       <c r="G278" s="18"/>
@@ -11455,7 +11455,7 @@
       <c r="A279" s="17"/>
       <c r="B279" s="18"/>
       <c r="C279" s="33"/>
-      <c r="D279" s="58"/>
+      <c r="D279" s="57"/>
       <c r="E279" s="19"/>
       <c r="F279" s="20"/>
       <c r="G279" s="18"/>
@@ -11483,7 +11483,7 @@
       <c r="A280" s="17"/>
       <c r="B280" s="18"/>
       <c r="C280" s="33"/>
-      <c r="D280" s="58"/>
+      <c r="D280" s="57"/>
       <c r="E280" s="19"/>
       <c r="F280" s="20"/>
       <c r="G280" s="18"/>
@@ -11511,7 +11511,7 @@
       <c r="A281" s="17"/>
       <c r="B281" s="18"/>
       <c r="C281" s="33"/>
-      <c r="D281" s="58"/>
+      <c r="D281" s="57"/>
       <c r="E281" s="19"/>
       <c r="F281" s="20"/>
       <c r="G281" s="18"/>
@@ -11539,7 +11539,7 @@
       <c r="A282" s="17"/>
       <c r="B282" s="18"/>
       <c r="C282" s="33"/>
-      <c r="D282" s="58"/>
+      <c r="D282" s="57"/>
       <c r="E282" s="19"/>
       <c r="F282" s="20"/>
       <c r="G282" s="18"/>
@@ -11567,7 +11567,7 @@
       <c r="A283" s="17"/>
       <c r="B283" s="18"/>
       <c r="C283" s="33"/>
-      <c r="D283" s="58"/>
+      <c r="D283" s="57"/>
       <c r="E283" s="19"/>
       <c r="F283" s="20"/>
       <c r="G283" s="18"/>
@@ -11595,7 +11595,7 @@
       <c r="A284" s="17"/>
       <c r="B284" s="18"/>
       <c r="C284" s="33"/>
-      <c r="D284" s="58"/>
+      <c r="D284" s="57"/>
       <c r="E284" s="19"/>
       <c r="F284" s="20"/>
       <c r="G284" s="18"/>
@@ -11623,7 +11623,7 @@
       <c r="A285" s="17"/>
       <c r="B285" s="18"/>
       <c r="C285" s="33"/>
-      <c r="D285" s="58"/>
+      <c r="D285" s="57"/>
       <c r="E285" s="19"/>
       <c r="F285" s="20"/>
       <c r="G285" s="18"/>
@@ -11651,7 +11651,7 @@
       <c r="A286" s="17"/>
       <c r="B286" s="18"/>
       <c r="C286" s="33"/>
-      <c r="D286" s="58"/>
+      <c r="D286" s="57"/>
       <c r="E286" s="19"/>
       <c r="F286" s="20"/>
       <c r="G286" s="18"/>
@@ -11679,7 +11679,7 @@
       <c r="A287" s="17"/>
       <c r="B287" s="18"/>
       <c r="C287" s="33"/>
-      <c r="D287" s="58"/>
+      <c r="D287" s="57"/>
       <c r="E287" s="19"/>
       <c r="F287" s="20"/>
       <c r="G287" s="18"/>
@@ -11707,7 +11707,7 @@
       <c r="A288" s="17"/>
       <c r="B288" s="18"/>
       <c r="C288" s="33"/>
-      <c r="D288" s="58"/>
+      <c r="D288" s="57"/>
       <c r="E288" s="19"/>
       <c r="F288" s="20"/>
       <c r="G288" s="18"/>
@@ -11735,7 +11735,7 @@
       <c r="A289" s="17"/>
       <c r="B289" s="18"/>
       <c r="C289" s="33"/>
-      <c r="D289" s="58"/>
+      <c r="D289" s="57"/>
       <c r="E289" s="19"/>
       <c r="F289" s="20"/>
       <c r="G289" s="18"/>
@@ -11763,7 +11763,7 @@
       <c r="A290" s="17"/>
       <c r="B290" s="18"/>
       <c r="C290" s="33"/>
-      <c r="D290" s="58"/>
+      <c r="D290" s="57"/>
       <c r="E290" s="19"/>
       <c r="F290" s="20"/>
       <c r="G290" s="18"/>
@@ -11791,7 +11791,7 @@
       <c r="A291" s="17"/>
       <c r="B291" s="18"/>
       <c r="C291" s="33"/>
-      <c r="D291" s="58"/>
+      <c r="D291" s="57"/>
       <c r="E291" s="19"/>
       <c r="F291" s="20"/>
       <c r="G291" s="18"/>
@@ -11819,7 +11819,7 @@
       <c r="A292" s="17"/>
       <c r="B292" s="18"/>
       <c r="C292" s="33"/>
-      <c r="D292" s="58"/>
+      <c r="D292" s="57"/>
       <c r="E292" s="19"/>
       <c r="F292" s="20"/>
       <c r="G292" s="18"/>
@@ -11847,7 +11847,7 @@
       <c r="A293" s="17"/>
       <c r="B293" s="18"/>
       <c r="C293" s="33"/>
-      <c r="D293" s="58"/>
+      <c r="D293" s="57"/>
       <c r="E293" s="19"/>
       <c r="F293" s="20"/>
       <c r="G293" s="18"/>
@@ -11875,7 +11875,7 @@
       <c r="A294" s="17"/>
       <c r="B294" s="18"/>
       <c r="C294" s="33"/>
-      <c r="D294" s="58"/>
+      <c r="D294" s="57"/>
       <c r="E294" s="19"/>
       <c r="F294" s="20"/>
       <c r="G294" s="18"/>
@@ -11903,7 +11903,7 @@
       <c r="A295" s="17"/>
       <c r="B295" s="18"/>
       <c r="C295" s="33"/>
-      <c r="D295" s="58"/>
+      <c r="D295" s="57"/>
       <c r="E295" s="19"/>
       <c r="F295" s="20"/>
       <c r="G295" s="18"/>
@@ -11931,7 +11931,7 @@
       <c r="A296" s="17"/>
       <c r="B296" s="18"/>
       <c r="C296" s="33"/>
-      <c r="D296" s="58"/>
+      <c r="D296" s="57"/>
       <c r="E296" s="19"/>
       <c r="F296" s="20"/>
       <c r="G296" s="18"/>
@@ -11959,7 +11959,7 @@
       <c r="A297" s="17"/>
       <c r="B297" s="18"/>
       <c r="C297" s="33"/>
-      <c r="D297" s="58"/>
+      <c r="D297" s="57"/>
       <c r="E297" s="19"/>
       <c r="F297" s="20"/>
       <c r="G297" s="18"/>
@@ -11987,7 +11987,7 @@
       <c r="A298" s="17"/>
       <c r="B298" s="18"/>
       <c r="C298" s="33"/>
-      <c r="D298" s="58"/>
+      <c r="D298" s="57"/>
       <c r="E298" s="19"/>
       <c r="F298" s="20"/>
       <c r="G298" s="18"/>
@@ -12015,7 +12015,7 @@
       <c r="A299" s="17"/>
       <c r="B299" s="18"/>
       <c r="C299" s="33"/>
-      <c r="D299" s="58"/>
+      <c r="D299" s="57"/>
       <c r="E299" s="19"/>
       <c r="F299" s="20"/>
       <c r="G299" s="18"/>
@@ -12043,7 +12043,7 @@
       <c r="A300" s="17"/>
       <c r="B300" s="18"/>
       <c r="C300" s="33"/>
-      <c r="D300" s="58"/>
+      <c r="D300" s="57"/>
       <c r="E300" s="19"/>
       <c r="F300" s="20"/>
       <c r="G300" s="18"/>
@@ -12071,7 +12071,7 @@
       <c r="A301" s="17"/>
       <c r="B301" s="18"/>
       <c r="C301" s="33"/>
-      <c r="D301" s="58"/>
+      <c r="D301" s="57"/>
       <c r="E301" s="19"/>
       <c r="F301" s="20"/>
       <c r="G301" s="18"/>
@@ -12099,7 +12099,7 @@
       <c r="A302" s="17"/>
       <c r="B302" s="18"/>
       <c r="C302" s="33"/>
-      <c r="D302" s="58"/>
+      <c r="D302" s="57"/>
       <c r="E302" s="19"/>
       <c r="F302" s="20"/>
       <c r="G302" s="18"/>
@@ -12127,7 +12127,7 @@
       <c r="A303" s="17"/>
       <c r="B303" s="18"/>
       <c r="C303" s="33"/>
-      <c r="D303" s="58"/>
+      <c r="D303" s="57"/>
       <c r="E303" s="19"/>
       <c r="F303" s="20"/>
       <c r="G303" s="18"/>
@@ -12155,7 +12155,7 @@
       <c r="A304" s="17"/>
       <c r="B304" s="18"/>
       <c r="C304" s="33"/>
-      <c r="D304" s="58"/>
+      <c r="D304" s="57"/>
       <c r="E304" s="19"/>
       <c r="F304" s="20"/>
       <c r="G304" s="18"/>
@@ -12183,7 +12183,7 @@
       <c r="A305" s="17"/>
       <c r="B305" s="18"/>
       <c r="C305" s="33"/>
-      <c r="D305" s="58"/>
+      <c r="D305" s="57"/>
       <c r="E305" s="19"/>
       <c r="F305" s="20"/>
       <c r="G305" s="18"/>
@@ -12211,7 +12211,7 @@
       <c r="A306" s="17"/>
       <c r="B306" s="18"/>
       <c r="C306" s="33"/>
-      <c r="D306" s="58"/>
+      <c r="D306" s="57"/>
       <c r="E306" s="19"/>
       <c r="F306" s="20"/>
       <c r="G306" s="18"/>
@@ -12239,7 +12239,7 @@
       <c r="A307" s="17"/>
       <c r="B307" s="18"/>
       <c r="C307" s="33"/>
-      <c r="D307" s="58"/>
+      <c r="D307" s="57"/>
       <c r="E307" s="19"/>
       <c r="F307" s="20"/>
       <c r="G307" s="18"/>
@@ -12267,7 +12267,7 @@
       <c r="A308" s="17"/>
       <c r="B308" s="18"/>
       <c r="C308" s="33"/>
-      <c r="D308" s="58"/>
+      <c r="D308" s="57"/>
       <c r="E308" s="19"/>
       <c r="F308" s="20"/>
       <c r="G308" s="18"/>
@@ -12295,7 +12295,7 @@
       <c r="A309" s="17"/>
       <c r="B309" s="18"/>
       <c r="C309" s="33"/>
-      <c r="D309" s="58"/>
+      <c r="D309" s="57"/>
       <c r="E309" s="19"/>
       <c r="F309" s="20"/>
       <c r="G309" s="18"/>
@@ -12323,7 +12323,7 @@
       <c r="A310" s="17"/>
       <c r="B310" s="18"/>
       <c r="C310" s="33"/>
-      <c r="D310" s="58"/>
+      <c r="D310" s="57"/>
       <c r="E310" s="19"/>
       <c r="F310" s="20"/>
       <c r="G310" s="18"/>
@@ -12351,7 +12351,7 @@
       <c r="A311" s="17"/>
       <c r="B311" s="18"/>
       <c r="C311" s="33"/>
-      <c r="D311" s="58"/>
+      <c r="D311" s="57"/>
       <c r="E311" s="19"/>
       <c r="F311" s="20"/>
       <c r="G311" s="18"/>
@@ -12379,7 +12379,7 @@
       <c r="A312" s="17"/>
       <c r="B312" s="18"/>
       <c r="C312" s="33"/>
-      <c r="D312" s="58"/>
+      <c r="D312" s="57"/>
       <c r="E312" s="19"/>
       <c r="F312" s="20"/>
       <c r="G312" s="18"/>
@@ -12407,7 +12407,7 @@
       <c r="A313" s="17"/>
       <c r="B313" s="18"/>
       <c r="C313" s="33"/>
-      <c r="D313" s="58"/>
+      <c r="D313" s="57"/>
       <c r="E313" s="19"/>
       <c r="F313" s="20"/>
       <c r="G313" s="18"/>
@@ -12432,7 +12432,7 @@
       <c r="Z313" s="22"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="x33DIPluUbwcJv8PaG6BqIDWV0Rxb8mtepRsiUW38Kmzn3n48z0SQoErJXgREOkyQupz+C4y/GmextyOsj2+fw==" saltValue="JoTK3qXNAWT2i8Yj/x/SXA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="kptRvdhRMze4GHgkwk24Q9wjGk4KQZ0N3ruqYEot5m7td6vAlCH/AYOb5G+6Uy748k+zxpkU+KkCE3XNZk7/pA==" saltValue="mY/URKkRVjrh8RO5EloZdA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A3:Z420" name="Rango1"/>
   </protectedRanges>
@@ -12497,8 +12497,8 @@
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="D3" s="1" t="s">
